--- a/research/traditional_assets/database/data/kuwait/kuwait_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1038361803435911</v>
+        <v>0.1037186760730757</v>
       </c>
       <c r="C2">
-        <v>1299.01501585673</v>
+        <v>1288.535654895065</v>
       </c>
       <c r="D2">
-        <v>1272.01501585673</v>
+        <v>1274.595654895065</v>
       </c>
       <c r="E2">
-        <v>-91.2</v>
+        <v>-78.14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.06</v>
       </c>
       <c r="G2">
         <v>27</v>
@@ -1451,28 +1451,28 @@
         <v>17.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.656918</v>
       </c>
       <c r="N2">
-        <v>17.75</v>
+        <v>17.093082</v>
       </c>
       <c r="O2">
-        <v>2.6625</v>
+        <v>2.5639623</v>
       </c>
       <c r="P2">
-        <v>15.0875</v>
+        <v>14.5291197</v>
       </c>
       <c r="Q2">
-        <v>21.0875</v>
+        <v>20.5291197</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1038361803435911</v>
+        <v>0.1043344707808845</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.110377280888253</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>27.02011514374701</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1037186760730757</v>
+        <v>0.1036011718025603</v>
       </c>
       <c r="C3">
-        <v>1288.535654895065</v>
+        <v>1278.066786319565</v>
       </c>
       <c r="D3">
-        <v>1274.595654895065</v>
+        <v>1277.186786319565</v>
       </c>
       <c r="E3">
-        <v>-78.14</v>
+        <v>-65.08</v>
       </c>
       <c r="F3">
-        <v>13.06</v>
+        <v>26.12</v>
       </c>
       <c r="G3">
         <v>27</v>
@@ -1533,28 +1533,28 @@
         <v>17.75</v>
       </c>
       <c r="M3">
-        <v>0.656918</v>
+        <v>1.313836</v>
       </c>
       <c r="N3">
-        <v>17.093082</v>
+        <v>16.436164</v>
       </c>
       <c r="O3">
-        <v>2.5639623</v>
+        <v>2.4654246</v>
       </c>
       <c r="P3">
-        <v>14.5291197</v>
+        <v>13.9707394</v>
       </c>
       <c r="Q3">
-        <v>20.5291197</v>
+        <v>19.9707394</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1043344707808845</v>
+        <v>0.1048429304107758</v>
       </c>
       <c r="T3">
-        <v>1.110377280888253</v>
+        <v>1.120022572179834</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>27.02011514374701</v>
+        <v>13.51005757187351</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1036011718025603</v>
+        <v>0.1035652675320449</v>
       </c>
       <c r="C4">
-        <v>1278.066786319565</v>
+        <v>1265.800627702698</v>
       </c>
       <c r="D4">
-        <v>1277.186786319565</v>
+        <v>1277.980627702698</v>
       </c>
       <c r="E4">
-        <v>-65.08</v>
+        <v>-52.02</v>
       </c>
       <c r="F4">
-        <v>26.12</v>
+        <v>39.18</v>
       </c>
       <c r="G4">
         <v>27</v>
@@ -1615,45 +1615,45 @@
         <v>17.75</v>
       </c>
       <c r="M4">
-        <v>1.313836</v>
+        <v>2.09613</v>
       </c>
       <c r="N4">
-        <v>16.436164</v>
+        <v>15.65387</v>
       </c>
       <c r="O4">
-        <v>2.4654246</v>
+        <v>2.3480805</v>
       </c>
       <c r="P4">
-        <v>13.9707394</v>
+        <v>13.3057895</v>
       </c>
       <c r="Q4">
-        <v>19.9707394</v>
+        <v>19.3057895</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1048429304107758</v>
+        <v>0.1053618737443762</v>
       </c>
       <c r="T4">
-        <v>1.120022572179834</v>
+        <v>1.129866735456807</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.15</v>
       </c>
       <c r="W4">
-        <v>0.04275499999999999</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>13.51005757187351</v>
+        <v>8.467986241311369</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1035652675320449</v>
+        <v>0.1035021632615295</v>
       </c>
       <c r="C5">
-        <v>1265.800627702698</v>
+        <v>1254.138253557355</v>
       </c>
       <c r="D5">
-        <v>1277.980627702698</v>
+        <v>1279.378253557355</v>
       </c>
       <c r="E5">
-        <v>-52.02</v>
+        <v>-38.96</v>
       </c>
       <c r="F5">
-        <v>39.18</v>
+        <v>52.24</v>
       </c>
       <c r="G5">
         <v>27</v>
@@ -1697,45 +1697,45 @@
         <v>17.75</v>
       </c>
       <c r="M5">
-        <v>2.09613</v>
+        <v>2.836632</v>
       </c>
       <c r="N5">
-        <v>15.65387</v>
+        <v>14.913368</v>
       </c>
       <c r="O5">
-        <v>2.3480805</v>
+        <v>2.2370052</v>
       </c>
       <c r="P5">
-        <v>13.3057895</v>
+        <v>12.6763628</v>
       </c>
       <c r="Q5">
-        <v>19.3057895</v>
+        <v>18.6763628</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1053618737443762</v>
+        <v>0.1058916283974266</v>
       </c>
       <c r="T5">
-        <v>1.129866735456807</v>
+        <v>1.139915985468718</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.15</v>
       </c>
       <c r="W5">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.467986241311369</v>
+        <v>6.257420772239755</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1035021632615295</v>
+        <v>0.1034611589910141</v>
       </c>
       <c r="C6">
-        <v>1254.138253557355</v>
+        <v>1241.988050948153</v>
       </c>
       <c r="D6">
-        <v>1279.378253557355</v>
+        <v>1280.288050948153</v>
       </c>
       <c r="E6">
-        <v>-38.96</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="F6">
-        <v>52.24</v>
+        <v>65.3</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -1779,45 +1779,45 @@
         <v>17.75</v>
       </c>
       <c r="M6">
-        <v>2.836632</v>
+        <v>3.61109</v>
       </c>
       <c r="N6">
-        <v>14.913368</v>
+        <v>14.13891</v>
       </c>
       <c r="O6">
-        <v>2.2370052</v>
+        <v>2.1208365</v>
       </c>
       <c r="P6">
-        <v>12.6763628</v>
+        <v>12.0180735</v>
       </c>
       <c r="Q6">
-        <v>18.6763628</v>
+        <v>18.0180735</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1058916283974266</v>
+        <v>0.1064325357800149</v>
       </c>
       <c r="T6">
-        <v>1.139915985468718</v>
+        <v>1.150176798638774</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.15</v>
       </c>
       <c r="W6">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.257420772239755</v>
+        <v>4.915413351647286</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1034611589910141</v>
+        <v>0.1036921547204987</v>
       </c>
       <c r="C7">
-        <v>1241.988050948153</v>
+        <v>1223.819568223558</v>
       </c>
       <c r="D7">
-        <v>1280.288050948153</v>
+        <v>1275.179568223558</v>
       </c>
       <c r="E7">
-        <v>-25.90000000000001</v>
+        <v>-12.84</v>
       </c>
       <c r="F7">
-        <v>65.3</v>
+        <v>78.36</v>
       </c>
       <c r="G7">
         <v>27</v>
@@ -1861,45 +1861,45 @@
         <v>17.75</v>
       </c>
       <c r="M7">
-        <v>3.61109</v>
+        <v>4.803468</v>
       </c>
       <c r="N7">
-        <v>14.13891</v>
+        <v>12.946532</v>
       </c>
       <c r="O7">
-        <v>2.1208365</v>
+        <v>1.9419798</v>
       </c>
       <c r="P7">
-        <v>12.0180735</v>
+        <v>11.0045522</v>
       </c>
       <c r="Q7">
-        <v>18.0180735</v>
+        <v>17.0045522</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1064325357800149</v>
+        <v>0.1069849518303178</v>
       </c>
       <c r="T7">
-        <v>1.150176798638774</v>
+        <v>1.160655926982662</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.15</v>
       </c>
       <c r="W7">
-        <v>0.047005</v>
+        <v>0.052105</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.915413351647286</v>
+        <v>3.695246850816952</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1036921547204987</v>
+        <v>0.1038347504499834</v>
       </c>
       <c r="C8">
-        <v>1223.819568223558</v>
+        <v>1207.626356495329</v>
       </c>
       <c r="D8">
-        <v>1275.179568223558</v>
+        <v>1272.04635649533</v>
       </c>
       <c r="E8">
-        <v>-12.84</v>
+        <v>0.2199999999999847</v>
       </c>
       <c r="F8">
-        <v>78.36</v>
+        <v>91.41999999999999</v>
       </c>
       <c r="G8">
         <v>27</v>
@@ -1943,45 +1943,45 @@
         <v>17.75</v>
       </c>
       <c r="M8">
-        <v>4.803468</v>
+        <v>5.860022</v>
       </c>
       <c r="N8">
-        <v>12.946532</v>
+        <v>11.889978</v>
       </c>
       <c r="O8">
-        <v>1.9419798</v>
+        <v>1.7834967</v>
       </c>
       <c r="P8">
-        <v>11.0045522</v>
+        <v>10.1064813</v>
       </c>
       <c r="Q8">
-        <v>17.0045522</v>
+        <v>16.1064813</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1069849518303178</v>
+        <v>0.107549247795681</v>
       </c>
       <c r="T8">
-        <v>1.160655926982662</v>
+        <v>1.171360412925342</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V8">
         <v>0.15</v>
       </c>
       <c r="W8">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.695246850816952</v>
+        <v>3.028998867239748</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1038347504499834</v>
+        <v>0.104630146179468</v>
       </c>
       <c r="C9">
-        <v>1207.626356495329</v>
+        <v>1177.368026976033</v>
       </c>
       <c r="D9">
-        <v>1272.04635649533</v>
+        <v>1254.848026976033</v>
       </c>
       <c r="E9">
-        <v>0.2199999999999989</v>
+        <v>13.28</v>
       </c>
       <c r="F9">
-        <v>91.42</v>
+        <v>104.48</v>
       </c>
       <c r="G9">
         <v>27</v>
@@ -2025,45 +2025,45 @@
         <v>17.75</v>
       </c>
       <c r="M9">
-        <v>5.860022000000001</v>
+        <v>7.919584000000001</v>
       </c>
       <c r="N9">
-        <v>11.889978</v>
+        <v>9.830416</v>
       </c>
       <c r="O9">
-        <v>1.7834967</v>
+        <v>1.4745624</v>
       </c>
       <c r="P9">
-        <v>10.1064813</v>
+        <v>8.3558536</v>
       </c>
       <c r="Q9">
-        <v>16.1064813</v>
+        <v>14.3558536</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.107549247795681</v>
+        <v>0.1081258110646391</v>
       </c>
       <c r="T9">
-        <v>1.171360412925342</v>
+        <v>1.182297605084168</v>
       </c>
       <c r="U9">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.054485</v>
+        <v>0.06443</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.028998867239747</v>
+        <v>2.241279339924925</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.104630146179468</v>
+        <v>0.1058156919089526</v>
       </c>
       <c r="C10">
-        <v>1177.368026976033</v>
+        <v>1139.519847881297</v>
       </c>
       <c r="D10">
-        <v>1254.848026976033</v>
+        <v>1230.059847881297</v>
       </c>
       <c r="E10">
-        <v>13.28</v>
+        <v>26.33999999999999</v>
       </c>
       <c r="F10">
-        <v>104.48</v>
+        <v>117.54</v>
       </c>
       <c r="G10">
         <v>27</v>
@@ -2107,45 +2107,45 @@
         <v>17.75</v>
       </c>
       <c r="M10">
-        <v>7.919584000000001</v>
+        <v>10.5786</v>
       </c>
       <c r="N10">
-        <v>9.830416</v>
+        <v>7.171400000000002</v>
       </c>
       <c r="O10">
-        <v>1.4745624</v>
+        <v>1.07571</v>
       </c>
       <c r="P10">
-        <v>8.3558536</v>
+        <v>6.095690000000002</v>
       </c>
       <c r="Q10">
-        <v>14.3558536</v>
+        <v>12.09569</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1081258110646391</v>
+        <v>0.108715046053794</v>
       </c>
       <c r="T10">
-        <v>1.182297605084168</v>
+        <v>1.193475175092638</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.15</v>
       </c>
       <c r="W10">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.241279339924925</v>
+        <v>1.677915792259846</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1058156919089526</v>
+        <v>0.1060356376384372</v>
       </c>
       <c r="C11">
-        <v>1139.519847881297</v>
+        <v>1121.968380352126</v>
       </c>
       <c r="D11">
-        <v>1230.059847881297</v>
+        <v>1225.568380352126</v>
       </c>
       <c r="E11">
-        <v>26.33999999999999</v>
+        <v>39.39999999999999</v>
       </c>
       <c r="F11">
-        <v>117.54</v>
+        <v>130.6</v>
       </c>
       <c r="G11">
         <v>27</v>
@@ -2189,28 +2189,28 @@
         <v>17.75</v>
       </c>
       <c r="M11">
-        <v>10.5786</v>
+        <v>11.754</v>
       </c>
       <c r="N11">
-        <v>7.171400000000002</v>
+        <v>5.996</v>
       </c>
       <c r="O11">
-        <v>1.07571</v>
+        <v>0.8994000000000001</v>
       </c>
       <c r="P11">
-        <v>6.095690000000002</v>
+        <v>5.0966</v>
       </c>
       <c r="Q11">
-        <v>12.09569</v>
+        <v>11.0966</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.108715046053794</v>
+        <v>0.1093173751538191</v>
       </c>
       <c r="T11">
-        <v>1.193475175092638</v>
+        <v>1.204901135545741</v>
       </c>
       <c r="U11">
         <v>0.09</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>1.677915792259846</v>
+        <v>1.510124213033861</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1060356376384372</v>
+        <v>0.1121015420457913</v>
       </c>
       <c r="C12">
-        <v>1121.968380352126</v>
+        <v>996.7815668496986</v>
       </c>
       <c r="D12">
-        <v>1225.568380352126</v>
+        <v>1113.441566849699</v>
       </c>
       <c r="E12">
-        <v>39.39999999999999</v>
+        <v>52.45999999999999</v>
       </c>
       <c r="F12">
-        <v>130.6</v>
+        <v>143.66</v>
       </c>
       <c r="G12">
         <v>27</v>
@@ -2271,45 +2271,45 @@
         <v>17.75</v>
       </c>
       <c r="M12">
-        <v>11.754</v>
+        <v>21.089288</v>
       </c>
       <c r="N12">
-        <v>5.996</v>
+        <v>-3.339288</v>
       </c>
       <c r="O12">
-        <v>0.8994000000000001</v>
+        <v>-0.5008931999999999</v>
       </c>
       <c r="P12">
-        <v>5.0966</v>
+        <v>-2.8383948</v>
       </c>
       <c r="Q12">
-        <v>11.0966</v>
+        <v>3.1616052</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1093173751538191</v>
+        <v>0.1101036064420079</v>
       </c>
       <c r="T12">
-        <v>1.204901135545741</v>
+        <v>1.219815652552246</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.15</v>
+        <v>0.1262489278917335</v>
       </c>
       <c r="W12">
-        <v>0.0765</v>
+        <v>0.1282666573854935</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.510124213033861</v>
+        <v>0.8416595192782231</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1121015420457913</v>
+        <v>0.1198082871302087</v>
       </c>
       <c r="C13">
-        <v>996.7815668496986</v>
+        <v>867.7749525603058</v>
       </c>
       <c r="D13">
-        <v>1113.441566849699</v>
+        <v>997.4949525603058</v>
       </c>
       <c r="E13">
-        <v>52.45999999999999</v>
+        <v>65.52</v>
       </c>
       <c r="F13">
-        <v>143.66</v>
+        <v>156.72</v>
       </c>
       <c r="G13">
         <v>27</v>
@@ -2353,45 +2353,45 @@
         <v>17.75</v>
       </c>
       <c r="M13">
-        <v>21.089288</v>
+        <v>31.469376</v>
       </c>
       <c r="N13">
-        <v>-3.339288</v>
+        <v>-13.719376</v>
       </c>
       <c r="O13">
-        <v>-0.5008931999999999</v>
+        <v>-2.0579064</v>
       </c>
       <c r="P13">
-        <v>-2.8383948</v>
+        <v>-11.6614696</v>
       </c>
       <c r="Q13">
-        <v>3.1616052</v>
+        <v>-5.6614696</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1101036064420079</v>
+        <v>0.1110806304747778</v>
       </c>
       <c r="T13">
-        <v>1.219815652552246</v>
+        <v>1.238349437421175</v>
       </c>
       <c r="U13">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.1262489278917335</v>
+        <v>0.08460606273222576</v>
       </c>
       <c r="W13">
-        <v>0.1282666573854935</v>
+        <v>0.1838111026033691</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.8416595192782231</v>
+        <v>0.5640404182148384</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1198082871302087</v>
+        <v>0.1213582871302087</v>
       </c>
       <c r="C14">
-        <v>867.7749525603058</v>
+        <v>834.2523767768702</v>
       </c>
       <c r="D14">
-        <v>997.4949525603058</v>
+        <v>977.0323767768701</v>
       </c>
       <c r="E14">
-        <v>65.52</v>
+        <v>78.58</v>
       </c>
       <c r="F14">
-        <v>156.72</v>
+        <v>169.78</v>
       </c>
       <c r="G14">
         <v>27</v>
@@ -2435,37 +2435,37 @@
         <v>17.75</v>
       </c>
       <c r="M14">
-        <v>31.469376</v>
+        <v>34.091824</v>
       </c>
       <c r="N14">
-        <v>-13.719376</v>
+        <v>-16.341824</v>
       </c>
       <c r="O14">
-        <v>-2.0579064</v>
+        <v>-2.4512736</v>
       </c>
       <c r="P14">
-        <v>-11.6614696</v>
+        <v>-13.8905504</v>
       </c>
       <c r="Q14">
-        <v>-5.6614696</v>
+        <v>-7.890550400000002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1110806304747778</v>
+        <v>0.1118309825492005</v>
       </c>
       <c r="T14">
-        <v>1.238349437421175</v>
+        <v>1.252583339000729</v>
       </c>
       <c r="U14">
         <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.08460606273222576</v>
+        <v>0.07809790406051609</v>
       </c>
       <c r="W14">
-        <v>0.1838111026033691</v>
+        <v>0.1851179408646484</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.5640404182148384</v>
+        <v>0.5206526937367739</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1213582871302087</v>
+        <v>0.1278957463897614</v>
       </c>
       <c r="C15">
-        <v>834.2523767768702</v>
+        <v>743.3892062189451</v>
       </c>
       <c r="D15">
-        <v>977.0323767768701</v>
+        <v>899.2292062189451</v>
       </c>
       <c r="E15">
-        <v>78.58</v>
+        <v>91.64</v>
       </c>
       <c r="F15">
-        <v>169.78</v>
+        <v>182.84</v>
       </c>
       <c r="G15">
         <v>27</v>
@@ -2517,45 +2517,45 @@
         <v>17.75</v>
       </c>
       <c r="M15">
-        <v>34.091824</v>
+        <v>43.113672</v>
       </c>
       <c r="N15">
-        <v>-16.341824</v>
+        <v>-25.363672</v>
       </c>
       <c r="O15">
-        <v>-2.4512736</v>
+        <v>-3.8045508</v>
       </c>
       <c r="P15">
-        <v>-13.8905504</v>
+        <v>-21.5591212</v>
       </c>
       <c r="Q15">
-        <v>-7.890550400000002</v>
+        <v>-15.5591212</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1118309825492005</v>
+        <v>0.112700481485299</v>
       </c>
       <c r="T15">
-        <v>1.252583339000729</v>
+        <v>1.269077412518783</v>
       </c>
       <c r="U15">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.07809790406051609</v>
+        <v>0.06175535222330401</v>
       </c>
       <c r="W15">
-        <v>0.1851179408646484</v>
+        <v>0.2212380879457449</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.5206526937367739</v>
+        <v>0.4117023481553601</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1278957463897614</v>
+        <v>0.1297957463897614</v>
       </c>
       <c r="C16">
-        <v>743.3892062189451</v>
+        <v>709.9884679643203</v>
       </c>
       <c r="D16">
-        <v>899.2292062189451</v>
+        <v>878.8884679643204</v>
       </c>
       <c r="E16">
-        <v>91.64</v>
+        <v>104.7</v>
       </c>
       <c r="F16">
-        <v>182.84</v>
+        <v>195.9</v>
       </c>
       <c r="G16">
         <v>27</v>
@@ -2599,37 +2599,37 @@
         <v>17.75</v>
       </c>
       <c r="M16">
-        <v>43.113672</v>
+        <v>46.19322000000001</v>
       </c>
       <c r="N16">
-        <v>-25.363672</v>
+        <v>-28.44322000000001</v>
       </c>
       <c r="O16">
-        <v>-3.8045508</v>
+        <v>-4.266483000000002</v>
       </c>
       <c r="P16">
-        <v>-21.5591212</v>
+        <v>-24.17673700000001</v>
       </c>
       <c r="Q16">
-        <v>-15.5591212</v>
+        <v>-18.17673700000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.112700481485299</v>
+        <v>0.1134875459733614</v>
       </c>
       <c r="T16">
-        <v>1.269077412518783</v>
+        <v>1.284007735019004</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.06175535222330401</v>
+        <v>0.05763832874175039</v>
       </c>
       <c r="W16">
-        <v>0.2212380879457449</v>
+        <v>0.2222088820826953</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.4117023481553601</v>
+        <v>0.3842555249450027</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1297957463897614</v>
+        <v>0.1316957463897614</v>
       </c>
       <c r="C17">
-        <v>709.9884679643204</v>
+        <v>677.4875973820342</v>
       </c>
       <c r="D17">
-        <v>878.8884679643204</v>
+        <v>859.4475973820342</v>
       </c>
       <c r="E17">
-        <v>104.7</v>
+        <v>117.76</v>
       </c>
       <c r="F17">
-        <v>195.9</v>
+        <v>208.96</v>
       </c>
       <c r="G17">
         <v>27</v>
@@ -2681,37 +2681,37 @@
         <v>17.75</v>
       </c>
       <c r="M17">
-        <v>46.19322</v>
+        <v>49.27276800000001</v>
       </c>
       <c r="N17">
-        <v>-28.44322</v>
+        <v>-31.52276800000001</v>
       </c>
       <c r="O17">
-        <v>-4.266483</v>
+        <v>-4.728415200000001</v>
       </c>
       <c r="P17">
-        <v>-24.176737</v>
+        <v>-26.79435280000001</v>
       </c>
       <c r="Q17">
-        <v>-18.176737</v>
+        <v>-20.79435280000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1134875459733614</v>
+        <v>0.1142933500920918</v>
       </c>
       <c r="T17">
-        <v>1.284007735019004</v>
+        <v>1.299293541388278</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.0576383287417504</v>
+        <v>0.054035933195391</v>
       </c>
       <c r="W17">
-        <v>0.2222088820826953</v>
+        <v>0.2230583269525268</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3842555249450027</v>
+        <v>0.36023955463594</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1316957463897614</v>
+        <v>0.1335957463897614</v>
       </c>
       <c r="C18">
-        <v>677.4875973820342</v>
+        <v>645.8281719864517</v>
       </c>
       <c r="D18">
-        <v>859.4475973820342</v>
+        <v>840.8481719864517</v>
       </c>
       <c r="E18">
-        <v>117.76</v>
+        <v>130.82</v>
       </c>
       <c r="F18">
-        <v>208.96</v>
+        <v>222.02</v>
       </c>
       <c r="G18">
         <v>27</v>
@@ -2763,37 +2763,37 @@
         <v>17.75</v>
       </c>
       <c r="M18">
-        <v>49.27276800000001</v>
+        <v>52.352316</v>
       </c>
       <c r="N18">
-        <v>-31.52276800000001</v>
+        <v>-34.602316</v>
       </c>
       <c r="O18">
-        <v>-4.728415200000001</v>
+        <v>-5.1903474</v>
       </c>
       <c r="P18">
-        <v>-26.79435280000001</v>
+        <v>-29.4119686</v>
       </c>
       <c r="Q18">
-        <v>-20.79435280000001</v>
+        <v>-23.4119686</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1142933500920918</v>
+        <v>0.1151185711775387</v>
       </c>
       <c r="T18">
-        <v>1.299293541388278</v>
+        <v>1.314947680441149</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.054035933195391</v>
+        <v>0.05085734888977977</v>
       </c>
       <c r="W18">
-        <v>0.2230583269525268</v>
+        <v>0.2238078371317899</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.36023955463594</v>
+        <v>0.3390489925985318</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1335957463897614</v>
+        <v>0.1354957463897614</v>
       </c>
       <c r="C19">
-        <v>645.8281719864517</v>
+        <v>614.9567194808666</v>
       </c>
       <c r="D19">
-        <v>840.8481719864517</v>
+        <v>823.0367194808666</v>
       </c>
       <c r="E19">
-        <v>130.82</v>
+        <v>143.8800000000001</v>
       </c>
       <c r="F19">
-        <v>222.02</v>
+        <v>235.08</v>
       </c>
       <c r="G19">
         <v>27</v>
@@ -2845,37 +2845,37 @@
         <v>17.75</v>
       </c>
       <c r="M19">
-        <v>52.352316</v>
+        <v>55.43186400000001</v>
       </c>
       <c r="N19">
-        <v>-34.602316</v>
+        <v>-37.68186400000001</v>
       </c>
       <c r="O19">
-        <v>-5.1903474</v>
+        <v>-5.652279600000002</v>
       </c>
       <c r="P19">
-        <v>-29.4119686</v>
+        <v>-32.02958440000001</v>
       </c>
       <c r="Q19">
-        <v>-23.4119686</v>
+        <v>-26.02958440000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1151185711775387</v>
+        <v>0.1159639196065331</v>
       </c>
       <c r="T19">
-        <v>1.314947680441149</v>
+        <v>1.330983627763602</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.05085734888977977</v>
+        <v>0.04803194061812533</v>
       </c>
       <c r="W19">
-        <v>0.2238078371317899</v>
+        <v>0.2244740684022461</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3390489925985318</v>
+        <v>0.3202129374541689</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1354957463897614</v>
+        <v>0.1373957463897615</v>
       </c>
       <c r="C20">
-        <v>614.9567194808662</v>
+        <v>584.8242043407041</v>
       </c>
       <c r="D20">
-        <v>823.0367194808663</v>
+        <v>805.9642043407041</v>
       </c>
       <c r="E20">
-        <v>143.88</v>
+        <v>156.94</v>
       </c>
       <c r="F20">
-        <v>235.08</v>
+        <v>248.14</v>
       </c>
       <c r="G20">
         <v>27</v>
@@ -2927,37 +2927,37 @@
         <v>17.75</v>
       </c>
       <c r="M20">
-        <v>55.431864</v>
+        <v>58.51141200000001</v>
       </c>
       <c r="N20">
-        <v>-37.681864</v>
+        <v>-40.76141200000001</v>
       </c>
       <c r="O20">
-        <v>-5.652279599999999</v>
+        <v>-6.114211800000001</v>
       </c>
       <c r="P20">
-        <v>-32.0295844</v>
+        <v>-34.64720020000001</v>
       </c>
       <c r="Q20">
-        <v>-26.0295844</v>
+        <v>-28.64720020000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1159639196065331</v>
+        <v>0.1168301408362434</v>
       </c>
       <c r="T20">
-        <v>1.330983627763602</v>
+        <v>1.347415524402659</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.04803194061812534</v>
+        <v>0.04550394374348716</v>
       </c>
       <c r="W20">
-        <v>0.2244740684022461</v>
+        <v>0.2250701700652857</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.320212937454169</v>
+        <v>0.3033596249565811</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1373957463897615</v>
+        <v>0.1392957463897614</v>
       </c>
       <c r="C21">
-        <v>584.8242043407041</v>
+        <v>555.3855769979846</v>
       </c>
       <c r="D21">
-        <v>805.9642043407041</v>
+        <v>789.5855769979845</v>
       </c>
       <c r="E21">
-        <v>156.94</v>
+        <v>170</v>
       </c>
       <c r="F21">
-        <v>248.14</v>
+        <v>261.2</v>
       </c>
       <c r="G21">
         <v>27</v>
@@ -3009,37 +3009,37 @@
         <v>17.75</v>
       </c>
       <c r="M21">
-        <v>58.51141200000001</v>
+        <v>61.59096</v>
       </c>
       <c r="N21">
-        <v>-40.76141200000001</v>
+        <v>-43.84096</v>
       </c>
       <c r="O21">
-        <v>-6.114211800000001</v>
+        <v>-6.576144</v>
       </c>
       <c r="P21">
-        <v>-34.64720020000001</v>
+        <v>-37.264816</v>
       </c>
       <c r="Q21">
-        <v>-28.64720020000001</v>
+        <v>-31.264816</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1168301408362434</v>
+        <v>0.1177180175966965</v>
       </c>
       <c r="T21">
-        <v>1.347415524402659</v>
+        <v>1.364258218457692</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.04550394374348716</v>
+        <v>0.04322874655631281</v>
       </c>
       <c r="W21">
-        <v>0.2250701700652857</v>
+        <v>0.2256066615620214</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3033596249565811</v>
+        <v>0.2881916437087521</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1392957463897614</v>
+        <v>0.1411957463897615</v>
       </c>
       <c r="C22">
-        <v>555.3855769979846</v>
+        <v>526.5993768992221</v>
       </c>
       <c r="D22">
-        <v>789.5855769979845</v>
+        <v>773.8593768992221</v>
       </c>
       <c r="E22">
-        <v>170</v>
+        <v>183.0600000000001</v>
       </c>
       <c r="F22">
-        <v>261.2</v>
+        <v>274.26</v>
       </c>
       <c r="G22">
         <v>27</v>
@@ -3091,37 +3091,37 @@
         <v>17.75</v>
       </c>
       <c r="M22">
-        <v>61.59096</v>
+        <v>64.67050800000001</v>
       </c>
       <c r="N22">
-        <v>-43.84096</v>
+        <v>-46.92050800000001</v>
       </c>
       <c r="O22">
-        <v>-6.576144</v>
+        <v>-7.038076200000002</v>
       </c>
       <c r="P22">
-        <v>-37.264816</v>
+        <v>-39.88243180000001</v>
       </c>
       <c r="Q22">
-        <v>-31.264816</v>
+        <v>-33.88243180000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1177180175966965</v>
+        <v>0.1186283722498192</v>
       </c>
       <c r="T22">
-        <v>1.364258218457692</v>
+        <v>1.381527309830574</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.04322874655631281</v>
+        <v>0.041170234815536</v>
       </c>
       <c r="W22">
-        <v>0.2256066615620214</v>
+        <v>0.2260920586304966</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2881916437087521</v>
+        <v>0.2744682321035733</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1411957463897614</v>
+        <v>0.1430957463897614</v>
       </c>
       <c r="C23">
-        <v>526.5993768992223</v>
+        <v>498.427382072455</v>
       </c>
       <c r="D23">
-        <v>773.8593768992223</v>
+        <v>758.747382072455</v>
       </c>
       <c r="E23">
-        <v>183.06</v>
+        <v>196.12</v>
       </c>
       <c r="F23">
-        <v>274.26</v>
+        <v>287.32</v>
       </c>
       <c r="G23">
         <v>27</v>
@@ -3173,37 +3173,37 @@
         <v>17.75</v>
       </c>
       <c r="M23">
-        <v>64.670508</v>
+        <v>67.750056</v>
       </c>
       <c r="N23">
-        <v>-46.920508</v>
+        <v>-50.000056</v>
       </c>
       <c r="O23">
-        <v>-7.0380762</v>
+        <v>-7.5000084</v>
       </c>
       <c r="P23">
-        <v>-39.8824318</v>
+        <v>-42.5000476</v>
       </c>
       <c r="Q23">
-        <v>-33.8824318</v>
+        <v>-36.5000476</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1186283722498192</v>
+        <v>0.1195620693299451</v>
       </c>
       <c r="T23">
-        <v>1.381527309830574</v>
+        <v>1.399239198418145</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.04117023481553601</v>
+        <v>0.03929886050573892</v>
       </c>
       <c r="W23">
-        <v>0.2260920586304966</v>
+        <v>0.2265333286927468</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2744682321035734</v>
+        <v>0.2619924033715928</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1430957463897614</v>
+        <v>0.1449957463897614</v>
       </c>
       <c r="C24">
-        <v>498.427382072455</v>
+        <v>470.8342989675282</v>
       </c>
       <c r="D24">
-        <v>758.747382072455</v>
+        <v>744.2142989675282</v>
       </c>
       <c r="E24">
-        <v>196.12</v>
+        <v>209.18</v>
       </c>
       <c r="F24">
-        <v>287.32</v>
+        <v>300.38</v>
       </c>
       <c r="G24">
         <v>27</v>
@@ -3255,37 +3255,37 @@
         <v>17.75</v>
       </c>
       <c r="M24">
-        <v>67.750056</v>
+        <v>70.829604</v>
       </c>
       <c r="N24">
-        <v>-50.000056</v>
+        <v>-53.079604</v>
       </c>
       <c r="O24">
-        <v>-7.5000084</v>
+        <v>-7.9619406</v>
       </c>
       <c r="P24">
-        <v>-42.5000476</v>
+        <v>-45.1176634</v>
       </c>
       <c r="Q24">
-        <v>-36.5000476</v>
+        <v>-39.1176634</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1195620693299451</v>
+        <v>0.120520018282282</v>
       </c>
       <c r="T24">
-        <v>1.399239198418145</v>
+        <v>1.417411136059939</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.03929886050573892</v>
+        <v>0.03759021439679374</v>
       </c>
       <c r="W24">
-        <v>0.2265333286927468</v>
+        <v>0.226936227445236</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2619924033715928</v>
+        <v>0.2506014293119583</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1449957463897614</v>
+        <v>0.1468957463897614</v>
       </c>
       <c r="C25">
-        <v>470.8342989675282</v>
+        <v>443.7874872713487</v>
       </c>
       <c r="D25">
-        <v>744.2142989675282</v>
+        <v>730.2274872713487</v>
       </c>
       <c r="E25">
-        <v>209.18</v>
+        <v>222.24</v>
       </c>
       <c r="F25">
-        <v>300.38</v>
+        <v>313.44</v>
       </c>
       <c r="G25">
         <v>27</v>
@@ -3337,37 +3337,37 @@
         <v>17.75</v>
       </c>
       <c r="M25">
-        <v>70.829604</v>
+        <v>73.90915200000001</v>
       </c>
       <c r="N25">
-        <v>-53.079604</v>
+        <v>-56.15915200000001</v>
       </c>
       <c r="O25">
-        <v>-7.9619406</v>
+        <v>-8.4238728</v>
       </c>
       <c r="P25">
-        <v>-45.1176634</v>
+        <v>-47.73527920000001</v>
       </c>
       <c r="Q25">
-        <v>-39.1176634</v>
+        <v>-41.73527920000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.120520018282282</v>
+        <v>0.1215031764175752</v>
       </c>
       <c r="T25">
-        <v>1.417411136059939</v>
+        <v>1.436061282587044</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.03759021439679374</v>
+        <v>0.03602395546359401</v>
       </c>
       <c r="W25">
-        <v>0.226936227445236</v>
+        <v>0.2273055513016845</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2506014293119583</v>
+        <v>0.2401597030906267</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1468957463897614</v>
+        <v>0.1487957463897615</v>
       </c>
       <c r="C26">
-        <v>443.7874872713487</v>
+        <v>417.2567151817404</v>
       </c>
       <c r="D26">
-        <v>730.2274872713487</v>
+        <v>716.7567151817404</v>
       </c>
       <c r="E26">
-        <v>222.24</v>
+        <v>235.3</v>
       </c>
       <c r="F26">
-        <v>313.44</v>
+        <v>326.5</v>
       </c>
       <c r="G26">
         <v>27</v>
@@ -3419,37 +3419,37 @@
         <v>17.75</v>
       </c>
       <c r="M26">
-        <v>73.90915200000001</v>
+        <v>76.98870000000001</v>
       </c>
       <c r="N26">
-        <v>-56.15915200000001</v>
+        <v>-59.23870000000001</v>
       </c>
       <c r="O26">
-        <v>-8.4238728</v>
+        <v>-8.885805000000001</v>
       </c>
       <c r="P26">
-        <v>-47.73527920000001</v>
+        <v>-50.352895</v>
       </c>
       <c r="Q26">
-        <v>-41.73527920000001</v>
+        <v>-44.352895</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1215031764175752</v>
+        <v>0.1225125521031429</v>
       </c>
       <c r="T26">
-        <v>1.436061282587044</v>
+        <v>1.455208766354871</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03602395546359401</v>
+        <v>0.03458299724505024</v>
       </c>
       <c r="W26">
-        <v>0.2273055513016845</v>
+        <v>0.2276453292496172</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2401597030906267</v>
+        <v>0.2305533149670016</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1487957463897615</v>
+        <v>0.1506957463897614</v>
       </c>
       <c r="C27">
-        <v>417.2567151817404</v>
+        <v>391.2139412779721</v>
       </c>
       <c r="D27">
-        <v>716.7567151817404</v>
+        <v>703.7739412779721</v>
       </c>
       <c r="E27">
-        <v>235.3</v>
+        <v>248.36</v>
       </c>
       <c r="F27">
-        <v>326.5</v>
+        <v>339.56</v>
       </c>
       <c r="G27">
         <v>27</v>
@@ -3501,37 +3501,37 @@
         <v>17.75</v>
       </c>
       <c r="M27">
-        <v>76.98870000000001</v>
+        <v>80.068248</v>
       </c>
       <c r="N27">
-        <v>-59.23870000000001</v>
+        <v>-62.318248</v>
       </c>
       <c r="O27">
-        <v>-8.885805000000001</v>
+        <v>-9.347737199999999</v>
       </c>
       <c r="P27">
-        <v>-50.352895</v>
+        <v>-52.9705108</v>
       </c>
       <c r="Q27">
-        <v>-44.352895</v>
+        <v>-46.9705108</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1225125521031429</v>
+        <v>0.1235492082126448</v>
       </c>
       <c r="T27">
-        <v>1.455208766354871</v>
+        <v>1.474873749683991</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03458299724505024</v>
+        <v>0.03325288196639447</v>
       </c>
       <c r="W27">
-        <v>0.2276453292496172</v>
+        <v>0.2279589704323242</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2305533149670016</v>
+        <v>0.2216858797759631</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1506957463897614</v>
+        <v>0.1525957463897614</v>
       </c>
       <c r="C28">
-        <v>391.2139412779721</v>
+        <v>365.6331196756956</v>
       </c>
       <c r="D28">
-        <v>703.7739412779721</v>
+        <v>691.2531196756956</v>
       </c>
       <c r="E28">
-        <v>248.36</v>
+        <v>261.42</v>
       </c>
       <c r="F28">
-        <v>339.56</v>
+        <v>352.62</v>
       </c>
       <c r="G28">
         <v>27</v>
@@ -3583,37 +3583,37 @@
         <v>17.75</v>
       </c>
       <c r="M28">
-        <v>80.068248</v>
+        <v>83.147796</v>
       </c>
       <c r="N28">
-        <v>-62.318248</v>
+        <v>-65.397796</v>
       </c>
       <c r="O28">
-        <v>-9.347737199999999</v>
+        <v>-9.809669399999999</v>
       </c>
       <c r="P28">
-        <v>-52.9705108</v>
+        <v>-55.5881266</v>
       </c>
       <c r="Q28">
-        <v>-46.9705108</v>
+        <v>-49.5881266</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1235492082126448</v>
+        <v>0.1246142658593934</v>
       </c>
       <c r="T28">
-        <v>1.474873749683991</v>
+        <v>1.495077499679662</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03325288196639447</v>
+        <v>0.03202129374541689</v>
       </c>
       <c r="W28">
-        <v>0.2279589704323242</v>
+        <v>0.2282493789348307</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2216858797759631</v>
+        <v>0.2134752916361127</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1525957463897614</v>
+        <v>0.1544957463897614</v>
       </c>
       <c r="C29">
-        <v>365.6331196756956</v>
+        <v>340.490025617219</v>
       </c>
       <c r="D29">
-        <v>691.2531196756956</v>
+        <v>679.170025617219</v>
       </c>
       <c r="E29">
-        <v>261.42</v>
+        <v>274.48</v>
       </c>
       <c r="F29">
-        <v>352.62</v>
+        <v>365.68</v>
       </c>
       <c r="G29">
         <v>27</v>
@@ -3665,37 +3665,37 @@
         <v>17.75</v>
       </c>
       <c r="M29">
-        <v>83.147796</v>
+        <v>86.227344</v>
       </c>
       <c r="N29">
-        <v>-65.397796</v>
+        <v>-68.477344</v>
       </c>
       <c r="O29">
-        <v>-9.809669399999999</v>
+        <v>-10.2716016</v>
       </c>
       <c r="P29">
-        <v>-55.5881266</v>
+        <v>-58.20574240000001</v>
       </c>
       <c r="Q29">
-        <v>-49.5881266</v>
+        <v>-52.20574240000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1246142658593934</v>
+        <v>0.1257089084407738</v>
       </c>
       <c r="T29">
-        <v>1.495077499679662</v>
+        <v>1.515842464952991</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03202129374541689</v>
+        <v>0.030877676111652</v>
       </c>
       <c r="W29">
-        <v>0.2282493789348307</v>
+        <v>0.2285190439728725</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2134752916361127</v>
+        <v>0.2058511740776801</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1544957463897614</v>
+        <v>0.1563957463897614</v>
       </c>
       <c r="C30">
-        <v>340.490025617219</v>
+        <v>315.7620990395997</v>
       </c>
       <c r="D30">
-        <v>679.170025617219</v>
+        <v>667.5020990395998</v>
       </c>
       <c r="E30">
-        <v>274.48</v>
+        <v>287.5400000000001</v>
       </c>
       <c r="F30">
-        <v>365.68</v>
+        <v>378.7400000000001</v>
       </c>
       <c r="G30">
         <v>27</v>
@@ -3747,37 +3747,37 @@
         <v>17.75</v>
       </c>
       <c r="M30">
-        <v>86.227344</v>
+        <v>89.30689200000002</v>
       </c>
       <c r="N30">
-        <v>-68.477344</v>
+        <v>-71.55689200000002</v>
       </c>
       <c r="O30">
-        <v>-10.2716016</v>
+        <v>-10.7335338</v>
       </c>
       <c r="P30">
-        <v>-58.20574240000001</v>
+        <v>-60.82335820000002</v>
       </c>
       <c r="Q30">
-        <v>-52.20574240000001</v>
+        <v>-54.82335820000002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1257089084407738</v>
+        <v>0.1268343860244467</v>
       </c>
       <c r="T30">
-        <v>1.515842464952991</v>
+        <v>1.537192358825568</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.030877676111652</v>
+        <v>0.02981292865952607</v>
       </c>
       <c r="W30">
-        <v>0.2285190439728725</v>
+        <v>0.2287701114220838</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2058511740776801</v>
+        <v>0.1987528577301738</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1563957463897614</v>
+        <v>0.1582957463897614</v>
       </c>
       <c r="C31">
-        <v>315.7620990395998</v>
+        <v>291.4283039951087</v>
       </c>
       <c r="D31">
-        <v>667.5020990395998</v>
+        <v>656.2283039951087</v>
       </c>
       <c r="E31">
-        <v>287.54</v>
+        <v>300.6</v>
       </c>
       <c r="F31">
-        <v>378.74</v>
+        <v>391.8</v>
       </c>
       <c r="G31">
         <v>27</v>
@@ -3829,37 +3829,37 @@
         <v>17.75</v>
       </c>
       <c r="M31">
-        <v>89.30689199999999</v>
+        <v>92.38644000000001</v>
       </c>
       <c r="N31">
-        <v>-71.55689199999999</v>
+        <v>-74.63644000000001</v>
       </c>
       <c r="O31">
-        <v>-10.7335338</v>
+        <v>-11.195466</v>
       </c>
       <c r="P31">
-        <v>-60.82335819999999</v>
+        <v>-63.440974</v>
       </c>
       <c r="Q31">
-        <v>-54.82335819999999</v>
+        <v>-57.440974</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1268343860244467</v>
+        <v>0.1279920201105102</v>
       </c>
       <c r="T31">
-        <v>1.537192358825568</v>
+        <v>1.559152249665934</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02981292865952608</v>
+        <v>0.0288191643708752</v>
       </c>
       <c r="W31">
-        <v>0.2287701114220838</v>
+        <v>0.2290044410413477</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1987528577301738</v>
+        <v>0.1921277624725014</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1582957463897614</v>
+        <v>0.1601957463897614</v>
       </c>
       <c r="C32">
-        <v>291.4283039951087</v>
+        <v>267.4690020810098</v>
       </c>
       <c r="D32">
-        <v>656.2283039951087</v>
+        <v>645.3290020810098</v>
       </c>
       <c r="E32">
-        <v>300.6</v>
+        <v>313.66</v>
       </c>
       <c r="F32">
-        <v>391.8</v>
+        <v>404.86</v>
       </c>
       <c r="G32">
         <v>27</v>
@@ -3911,37 +3911,37 @@
         <v>17.75</v>
       </c>
       <c r="M32">
-        <v>92.38644000000001</v>
+        <v>95.46598800000001</v>
       </c>
       <c r="N32">
-        <v>-74.63644000000001</v>
+        <v>-77.71598800000001</v>
       </c>
       <c r="O32">
-        <v>-11.195466</v>
+        <v>-11.6573982</v>
       </c>
       <c r="P32">
-        <v>-63.440974</v>
+        <v>-66.05858980000001</v>
       </c>
       <c r="Q32">
-        <v>-57.440974</v>
+        <v>-60.05858980000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1279920201105102</v>
+        <v>0.129183208807764</v>
       </c>
       <c r="T32">
-        <v>1.559152249665934</v>
+        <v>1.581748659081382</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0288191643708752</v>
+        <v>0.02788951390729858</v>
       </c>
       <c r="W32">
-        <v>0.2290044410413477</v>
+        <v>0.229223652620659</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1921277624725014</v>
+        <v>0.1859300927153239</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1601957463897614</v>
+        <v>0.1620957463897614</v>
       </c>
       <c r="C33">
-        <v>267.4690020810098</v>
+        <v>243.865838276509</v>
       </c>
       <c r="D33">
-        <v>645.3290020810098</v>
+        <v>634.785838276509</v>
       </c>
       <c r="E33">
-        <v>313.66</v>
+        <v>326.72</v>
       </c>
       <c r="F33">
-        <v>404.86</v>
+        <v>417.92</v>
       </c>
       <c r="G33">
         <v>27</v>
@@ -3993,37 +3993,37 @@
         <v>17.75</v>
       </c>
       <c r="M33">
-        <v>95.46598800000001</v>
+        <v>98.54553600000001</v>
       </c>
       <c r="N33">
-        <v>-77.71598800000001</v>
+        <v>-80.79553600000001</v>
       </c>
       <c r="O33">
-        <v>-11.6573982</v>
+        <v>-12.1193304</v>
       </c>
       <c r="P33">
-        <v>-66.05858980000001</v>
+        <v>-68.67620560000002</v>
       </c>
       <c r="Q33">
-        <v>-60.05858980000001</v>
+        <v>-62.67620560000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.129183208807764</v>
+        <v>0.1304094324667017</v>
       </c>
       <c r="T33">
-        <v>1.581748659081382</v>
+        <v>1.605009668773755</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02788951390729858</v>
+        <v>0.0270179665976955</v>
       </c>
       <c r="W33">
-        <v>0.229223652620659</v>
+        <v>0.2294291634762634</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1859300927153239</v>
+        <v>0.18011977731797</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1620957463897614</v>
+        <v>0.1639957463897614</v>
       </c>
       <c r="C34">
-        <v>243.865838276509</v>
+        <v>220.6016377907473</v>
       </c>
       <c r="D34">
-        <v>634.785838276509</v>
+        <v>624.5816377907473</v>
       </c>
       <c r="E34">
-        <v>326.72</v>
+        <v>339.78</v>
       </c>
       <c r="F34">
-        <v>417.92</v>
+        <v>430.98</v>
       </c>
       <c r="G34">
         <v>27</v>
@@ -4075,37 +4075,37 @@
         <v>17.75</v>
       </c>
       <c r="M34">
-        <v>98.54553600000001</v>
+        <v>101.625084</v>
       </c>
       <c r="N34">
-        <v>-80.79553600000001</v>
+        <v>-83.87508400000002</v>
       </c>
       <c r="O34">
-        <v>-12.1193304</v>
+        <v>-12.5812626</v>
       </c>
       <c r="P34">
-        <v>-68.67620560000002</v>
+        <v>-71.29382140000001</v>
       </c>
       <c r="Q34">
-        <v>-62.67620560000002</v>
+        <v>-65.29382140000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1304094324667017</v>
+        <v>0.131672259816951</v>
       </c>
       <c r="T34">
-        <v>1.605009668773755</v>
+        <v>1.628965036964408</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0270179665976955</v>
+        <v>0.02619924033715927</v>
       </c>
       <c r="W34">
-        <v>0.2294291634762634</v>
+        <v>0.2296222191284979</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.18011977731797</v>
+        <v>0.1746616022477285</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1639957463897614</v>
+        <v>0.1658957463897615</v>
       </c>
       <c r="C35">
-        <v>220.6016377907473</v>
+        <v>197.660312702421</v>
       </c>
       <c r="D35">
-        <v>624.5816377907473</v>
+        <v>614.700312702421</v>
       </c>
       <c r="E35">
-        <v>339.78</v>
+        <v>352.84</v>
       </c>
       <c r="F35">
-        <v>430.98</v>
+        <v>444.04</v>
       </c>
       <c r="G35">
         <v>27</v>
@@ -4157,37 +4157,37 @@
         <v>17.75</v>
       </c>
       <c r="M35">
-        <v>101.625084</v>
+        <v>104.704632</v>
       </c>
       <c r="N35">
-        <v>-83.87508400000002</v>
+        <v>-86.954632</v>
       </c>
       <c r="O35">
-        <v>-12.5812626</v>
+        <v>-13.0431948</v>
       </c>
       <c r="P35">
-        <v>-71.29382140000001</v>
+        <v>-73.91143720000001</v>
       </c>
       <c r="Q35">
-        <v>-65.29382140000001</v>
+        <v>-67.91143720000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.131672259816951</v>
+        <v>0.1329733546626624</v>
       </c>
       <c r="T35">
-        <v>1.628965036964408</v>
+        <v>1.653646325403263</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02619924033715927</v>
+        <v>0.02542867444488989</v>
       </c>
       <c r="W35">
-        <v>0.2296222191284979</v>
+        <v>0.229803918565895</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1746616022477285</v>
+        <v>0.1695244962992659</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1658957463897615</v>
+        <v>0.1677957463897614</v>
       </c>
       <c r="C36">
-        <v>197.660312702421</v>
+        <v>175.0267773235464</v>
       </c>
       <c r="D36">
-        <v>614.700312702421</v>
+        <v>605.1267773235464</v>
       </c>
       <c r="E36">
-        <v>352.84</v>
+        <v>365.9</v>
       </c>
       <c r="F36">
-        <v>444.04</v>
+        <v>457.1</v>
       </c>
       <c r="G36">
         <v>27</v>
@@ -4239,37 +4239,37 @@
         <v>17.75</v>
       </c>
       <c r="M36">
-        <v>104.704632</v>
+        <v>107.78418</v>
       </c>
       <c r="N36">
-        <v>-86.954632</v>
+        <v>-90.03418000000001</v>
       </c>
       <c r="O36">
-        <v>-13.0431948</v>
+        <v>-13.505127</v>
       </c>
       <c r="P36">
-        <v>-73.91143720000001</v>
+        <v>-76.529053</v>
       </c>
       <c r="Q36">
-        <v>-67.91143720000001</v>
+        <v>-70.529053</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1329733546626624</v>
+        <v>0.1343144831959341</v>
       </c>
       <c r="T36">
-        <v>1.653646325403263</v>
+        <v>1.679087038101775</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02542867444488989</v>
+        <v>0.0247021408893216</v>
       </c>
       <c r="W36">
-        <v>0.229803918565895</v>
+        <v>0.229975235178298</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1695244962992659</v>
+        <v>0.164680939262144</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1677957463897614</v>
+        <v>0.1696957463897614</v>
       </c>
       <c r="C37">
-        <v>175.0267773235464</v>
+        <v>152.6868713508442</v>
       </c>
       <c r="D37">
-        <v>605.1267773235464</v>
+        <v>595.8468713508443</v>
       </c>
       <c r="E37">
-        <v>365.9</v>
+        <v>378.9600000000001</v>
       </c>
       <c r="F37">
-        <v>457.1</v>
+        <v>470.1600000000001</v>
       </c>
       <c r="G37">
         <v>27</v>
@@ -4321,37 +4321,37 @@
         <v>17.75</v>
       </c>
       <c r="M37">
-        <v>107.78418</v>
+        <v>110.863728</v>
       </c>
       <c r="N37">
-        <v>-90.03418000000001</v>
+        <v>-93.11372800000002</v>
       </c>
       <c r="O37">
-        <v>-13.505127</v>
+        <v>-13.9670592</v>
       </c>
       <c r="P37">
-        <v>-76.529053</v>
+        <v>-79.14666880000001</v>
       </c>
       <c r="Q37">
-        <v>-70.529053</v>
+        <v>-73.14666880000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1343144831959341</v>
+        <v>0.1356975219958706</v>
       </c>
       <c r="T37">
-        <v>1.679087038101775</v>
+        <v>1.705322773072115</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0247021408893216</v>
+        <v>0.02401597030906267</v>
       </c>
       <c r="W37">
-        <v>0.229975235178298</v>
+        <v>0.230137034201123</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.164680939262144</v>
+        <v>0.1601064687270844</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1696957463897614</v>
+        <v>0.1715957463897614</v>
       </c>
       <c r="C38">
-        <v>152.6868713508443</v>
+        <v>130.6272899813844</v>
       </c>
       <c r="D38">
-        <v>595.8468713508443</v>
+        <v>586.8472899813844</v>
       </c>
       <c r="E38">
-        <v>378.96</v>
+        <v>392.02</v>
       </c>
       <c r="F38">
-        <v>470.16</v>
+        <v>483.22</v>
       </c>
       <c r="G38">
         <v>27</v>
@@ -4403,37 +4403,37 @@
         <v>17.75</v>
       </c>
       <c r="M38">
-        <v>110.863728</v>
+        <v>113.943276</v>
       </c>
       <c r="N38">
-        <v>-93.11372799999999</v>
+        <v>-96.193276</v>
       </c>
       <c r="O38">
-        <v>-13.9670592</v>
+        <v>-14.4289914</v>
       </c>
       <c r="P38">
-        <v>-79.1466688</v>
+        <v>-81.7642846</v>
       </c>
       <c r="Q38">
-        <v>-73.1466688</v>
+        <v>-75.7642846</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1356975219958705</v>
+        <v>0.1371244667894558</v>
       </c>
       <c r="T38">
-        <v>1.705322773072115</v>
+        <v>1.732391388517704</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02401597030906267</v>
+        <v>0.02336689003043935</v>
       </c>
       <c r="W38">
-        <v>0.230137034201123</v>
+        <v>0.2302900873308224</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1601064687270844</v>
+        <v>0.1557792668695958</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1715957463897614</v>
+        <v>0.1734957463897615</v>
       </c>
       <c r="C39">
-        <v>130.6272899813844</v>
+        <v>108.8355202671345</v>
       </c>
       <c r="D39">
-        <v>586.8472899813844</v>
+        <v>578.1155202671346</v>
       </c>
       <c r="E39">
-        <v>392.02</v>
+        <v>405.08</v>
       </c>
       <c r="F39">
-        <v>483.22</v>
+        <v>496.28</v>
       </c>
       <c r="G39">
         <v>27</v>
@@ -4485,37 +4485,37 @@
         <v>17.75</v>
       </c>
       <c r="M39">
-        <v>113.943276</v>
+        <v>117.022824</v>
       </c>
       <c r="N39">
-        <v>-96.193276</v>
+        <v>-99.27282400000001</v>
       </c>
       <c r="O39">
-        <v>-14.4289914</v>
+        <v>-14.8909236</v>
       </c>
       <c r="P39">
-        <v>-81.7642846</v>
+        <v>-84.38190040000001</v>
       </c>
       <c r="Q39">
-        <v>-75.7642846</v>
+        <v>-78.38190040000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1371244667894558</v>
+        <v>0.1385974420602535</v>
       </c>
       <c r="T39">
-        <v>1.732391388517704</v>
+        <v>1.760333185106699</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02336689003043935</v>
+        <v>0.02275197187174358</v>
       </c>
       <c r="W39">
-        <v>0.2302900873308224</v>
+        <v>0.2304350850326429</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1557792668695958</v>
+        <v>0.1516798124782905</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1734957463897615</v>
+        <v>0.1753957463897614</v>
       </c>
       <c r="C40">
-        <v>108.8355202671345</v>
+        <v>87.29978306813712</v>
       </c>
       <c r="D40">
-        <v>578.1155202671346</v>
+        <v>569.6397830681371</v>
       </c>
       <c r="E40">
-        <v>405.08</v>
+        <v>418.14</v>
       </c>
       <c r="F40">
-        <v>496.28</v>
+        <v>509.34</v>
       </c>
       <c r="G40">
         <v>27</v>
@@ -4567,37 +4567,37 @@
         <v>17.75</v>
       </c>
       <c r="M40">
-        <v>117.022824</v>
+        <v>120.102372</v>
       </c>
       <c r="N40">
-        <v>-99.27282400000001</v>
+        <v>-102.352372</v>
       </c>
       <c r="O40">
-        <v>-14.8909236</v>
+        <v>-15.3528558</v>
       </c>
       <c r="P40">
-        <v>-84.38190040000001</v>
+        <v>-86.99951620000002</v>
       </c>
       <c r="Q40">
-        <v>-78.38190040000001</v>
+        <v>-80.99951620000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1385974420602535</v>
+        <v>0.1401187116022248</v>
       </c>
       <c r="T40">
-        <v>1.760333185106699</v>
+        <v>1.789191106174022</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02275197187174358</v>
+        <v>0.02216858797759631</v>
       </c>
       <c r="W40">
-        <v>0.2304350850326429</v>
+        <v>0.2305726469548828</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1516798124782905</v>
+        <v>0.1477905865173087</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1753957463897614</v>
+        <v>0.1772957463897615</v>
       </c>
       <c r="C41">
-        <v>87.29978306813712</v>
+        <v>66.00898003804184</v>
       </c>
       <c r="D41">
-        <v>569.6397830681371</v>
+        <v>561.4089800380418</v>
       </c>
       <c r="E41">
-        <v>418.14</v>
+        <v>431.2</v>
       </c>
       <c r="F41">
-        <v>509.34</v>
+        <v>522.4</v>
       </c>
       <c r="G41">
         <v>27</v>
@@ -4649,37 +4649,37 @@
         <v>17.75</v>
       </c>
       <c r="M41">
-        <v>120.102372</v>
+        <v>123.18192</v>
       </c>
       <c r="N41">
-        <v>-102.352372</v>
+        <v>-105.43192</v>
       </c>
       <c r="O41">
-        <v>-15.3528558</v>
+        <v>-15.814788</v>
       </c>
       <c r="P41">
-        <v>-86.99951620000002</v>
+        <v>-89.617132</v>
       </c>
       <c r="Q41">
-        <v>-80.99951620000002</v>
+        <v>-83.617132</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1401187116022248</v>
+        <v>0.1416906901289286</v>
       </c>
       <c r="T41">
-        <v>1.789191106174022</v>
+        <v>1.819010957943589</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02216858797759631</v>
+        <v>0.0216143732781564</v>
       </c>
       <c r="W41">
-        <v>0.2305726469548828</v>
+        <v>0.2307033307810107</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1477905865173087</v>
+        <v>0.144095821854376</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1772957463897615</v>
+        <v>0.1791957463897614</v>
       </c>
       <c r="C42">
-        <v>66.00898003804184</v>
+        <v>44.95264514025882</v>
       </c>
       <c r="D42">
-        <v>561.4089800380418</v>
+        <v>553.4126451402589</v>
       </c>
       <c r="E42">
-        <v>431.2</v>
+        <v>444.26</v>
       </c>
       <c r="F42">
-        <v>522.4</v>
+        <v>535.46</v>
       </c>
       <c r="G42">
         <v>27</v>
@@ -4731,37 +4731,37 @@
         <v>17.75</v>
       </c>
       <c r="M42">
-        <v>123.18192</v>
+        <v>126.261468</v>
       </c>
       <c r="N42">
-        <v>-105.43192</v>
+        <v>-108.511468</v>
       </c>
       <c r="O42">
-        <v>-15.814788</v>
+        <v>-16.2767202</v>
       </c>
       <c r="P42">
-        <v>-89.617132</v>
+        <v>-92.23474780000001</v>
       </c>
       <c r="Q42">
-        <v>-83.617132</v>
+        <v>-86.23474780000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1416906901289286</v>
+        <v>0.1433159560633172</v>
       </c>
       <c r="T42">
-        <v>1.819010957943589</v>
+        <v>1.849841652146023</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0216143732781564</v>
+        <v>0.02108719344210381</v>
       </c>
       <c r="W42">
-        <v>0.2307033307810107</v>
+        <v>0.2308276397863519</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.144095821854376</v>
+        <v>0.1405812896140254</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1791957463897614</v>
+        <v>0.1810957463897614</v>
       </c>
       <c r="C43">
-        <v>44.95264514025882</v>
+        <v>24.12090024934855</v>
       </c>
       <c r="D43">
-        <v>553.4126451402589</v>
+        <v>545.6409002493486</v>
       </c>
       <c r="E43">
-        <v>444.26</v>
+        <v>457.3200000000001</v>
       </c>
       <c r="F43">
-        <v>535.46</v>
+        <v>548.5200000000001</v>
       </c>
       <c r="G43">
         <v>27</v>
@@ -4813,37 +4813,37 @@
         <v>17.75</v>
       </c>
       <c r="M43">
-        <v>126.261468</v>
+        <v>129.341016</v>
       </c>
       <c r="N43">
-        <v>-108.511468</v>
+        <v>-111.591016</v>
       </c>
       <c r="O43">
-        <v>-16.2767202</v>
+        <v>-16.7386524</v>
       </c>
       <c r="P43">
-        <v>-92.23474780000001</v>
+        <v>-94.85236360000002</v>
       </c>
       <c r="Q43">
-        <v>-86.23474780000001</v>
+        <v>-88.85236360000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1433159560633172</v>
+        <v>0.1449972656506158</v>
       </c>
       <c r="T43">
-        <v>1.849841652146023</v>
+        <v>1.881735473734747</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02108719344210381</v>
+        <v>0.020585117407768</v>
       </c>
       <c r="W43">
-        <v>0.2308276397863519</v>
+        <v>0.2309460293152483</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1405812896140254</v>
+        <v>0.1372341160517867</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1810957463897614</v>
+        <v>0.1829957463897615</v>
       </c>
       <c r="C44">
-        <v>24.12090024934867</v>
+        <v>3.504414441628796</v>
       </c>
       <c r="D44">
-        <v>545.6409002493486</v>
+        <v>538.0844144416288</v>
       </c>
       <c r="E44">
-        <v>457.32</v>
+        <v>470.3800000000001</v>
       </c>
       <c r="F44">
-        <v>548.52</v>
+        <v>561.58</v>
       </c>
       <c r="G44">
         <v>27</v>
@@ -4895,37 +4895,37 @@
         <v>17.75</v>
       </c>
       <c r="M44">
-        <v>129.341016</v>
+        <v>132.420564</v>
       </c>
       <c r="N44">
-        <v>-111.591016</v>
+        <v>-114.670564</v>
       </c>
       <c r="O44">
-        <v>-16.7386524</v>
+        <v>-17.2005846</v>
       </c>
       <c r="P44">
-        <v>-94.85236359999999</v>
+        <v>-97.46997940000001</v>
       </c>
       <c r="Q44">
-        <v>-88.85236359999999</v>
+        <v>-91.46997940000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1449972656506158</v>
+        <v>0.1467375685567669</v>
       </c>
       <c r="T44">
-        <v>1.881735473734747</v>
+        <v>1.914748376782725</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.020585117407768</v>
+        <v>0.02010639374712224</v>
       </c>
       <c r="W44">
-        <v>0.2309460293152483</v>
+        <v>0.2310589123544286</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1372341160517867</v>
+        <v>0.1340426249808149</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1829957463897615</v>
+        <v>0.1848957463897615</v>
       </c>
       <c r="C45">
-        <v>3.504414441628796</v>
+        <v>-16.90563337776541</v>
       </c>
       <c r="D45">
-        <v>538.0844144416288</v>
+        <v>530.7343666222346</v>
       </c>
       <c r="E45">
-        <v>470.3800000000001</v>
+        <v>483.44</v>
       </c>
       <c r="F45">
-        <v>561.58</v>
+        <v>574.64</v>
       </c>
       <c r="G45">
         <v>27</v>
@@ -4977,37 +4977,37 @@
         <v>17.75</v>
       </c>
       <c r="M45">
-        <v>132.420564</v>
+        <v>135.500112</v>
       </c>
       <c r="N45">
-        <v>-114.670564</v>
+        <v>-117.750112</v>
       </c>
       <c r="O45">
-        <v>-17.2005846</v>
+        <v>-17.6625168</v>
       </c>
       <c r="P45">
-        <v>-97.46997940000001</v>
+        <v>-100.0875952</v>
       </c>
       <c r="Q45">
-        <v>-91.46997940000001</v>
+        <v>-94.08759520000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1467375685567669</v>
+        <v>0.1485400251381378</v>
       </c>
       <c r="T45">
-        <v>1.914748376782725</v>
+        <v>1.948940312082417</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02010639374712224</v>
+        <v>0.01964943025286946</v>
       </c>
       <c r="W45">
-        <v>0.2310589123544286</v>
+        <v>0.2311666643463734</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1340426249808149</v>
+        <v>0.1309962016857964</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1848957463897615</v>
+        <v>0.1867957463897615</v>
       </c>
       <c r="C46">
-        <v>-16.90563337776541</v>
+        <v>-37.11758882608592</v>
       </c>
       <c r="D46">
-        <v>530.7343666222346</v>
+        <v>523.5824111739141</v>
       </c>
       <c r="E46">
-        <v>483.44</v>
+        <v>496.5000000000001</v>
       </c>
       <c r="F46">
-        <v>574.64</v>
+        <v>587.7</v>
       </c>
       <c r="G46">
         <v>27</v>
@@ -5059,37 +5059,37 @@
         <v>17.75</v>
       </c>
       <c r="M46">
-        <v>135.500112</v>
+        <v>138.57966</v>
       </c>
       <c r="N46">
-        <v>-117.750112</v>
+        <v>-120.82966</v>
       </c>
       <c r="O46">
-        <v>-17.6625168</v>
+        <v>-18.124449</v>
       </c>
       <c r="P46">
-        <v>-100.0875952</v>
+        <v>-102.705211</v>
       </c>
       <c r="Q46">
-        <v>-94.08759520000001</v>
+        <v>-96.70521100000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1485400251381378</v>
+        <v>0.1504080255951948</v>
       </c>
       <c r="T46">
-        <v>1.948940312082417</v>
+        <v>1.984375590483915</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01964943025286946</v>
+        <v>0.01921277624725013</v>
       </c>
       <c r="W46">
-        <v>0.2311666643463734</v>
+        <v>0.2312696273608984</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1309962016857964</v>
+        <v>0.1280851749816676</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1867957463897615</v>
+        <v>0.1886957463897614</v>
       </c>
       <c r="C47">
-        <v>-37.11758882608592</v>
+        <v>-57.13935365368957</v>
       </c>
       <c r="D47">
-        <v>523.5824111739141</v>
+        <v>516.6206463463104</v>
       </c>
       <c r="E47">
-        <v>496.5000000000001</v>
+        <v>509.56</v>
       </c>
       <c r="F47">
-        <v>587.7</v>
+        <v>600.76</v>
       </c>
       <c r="G47">
         <v>27</v>
@@ -5141,37 +5141,37 @@
         <v>17.75</v>
       </c>
       <c r="M47">
-        <v>138.57966</v>
+        <v>141.659208</v>
       </c>
       <c r="N47">
-        <v>-120.82966</v>
+        <v>-123.909208</v>
       </c>
       <c r="O47">
-        <v>-18.124449</v>
+        <v>-18.5863812</v>
       </c>
       <c r="P47">
-        <v>-102.705211</v>
+        <v>-105.3228268</v>
       </c>
       <c r="Q47">
-        <v>-96.70521100000002</v>
+        <v>-99.3228268</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1504080255951948</v>
+        <v>0.1523452112543651</v>
       </c>
       <c r="T47">
-        <v>1.984375590483915</v>
+        <v>2.021123286603988</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01921277624725013</v>
+        <v>0.01879510719839687</v>
       </c>
       <c r="W47">
-        <v>0.2312696273608984</v>
+        <v>0.231368113722618</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1280851749816676</v>
+        <v>0.1253007146559791</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1886957463897614</v>
+        <v>0.1905957463897615</v>
       </c>
       <c r="C48">
-        <v>-57.13935365368957</v>
+        <v>-76.97841486599748</v>
       </c>
       <c r="D48">
-        <v>516.6206463463104</v>
+        <v>509.8415851340026</v>
       </c>
       <c r="E48">
-        <v>509.56</v>
+        <v>522.62</v>
       </c>
       <c r="F48">
-        <v>600.76</v>
+        <v>613.8200000000001</v>
       </c>
       <c r="G48">
         <v>27</v>
@@ -5223,37 +5223,37 @@
         <v>17.75</v>
       </c>
       <c r="M48">
-        <v>141.659208</v>
+        <v>144.738756</v>
       </c>
       <c r="N48">
-        <v>-123.909208</v>
+        <v>-126.988756</v>
       </c>
       <c r="O48">
-        <v>-18.5863812</v>
+        <v>-19.0483134</v>
       </c>
       <c r="P48">
-        <v>-105.3228268</v>
+        <v>-107.9404426</v>
       </c>
       <c r="Q48">
-        <v>-99.3228268</v>
+        <v>-101.9404426</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1523452112543651</v>
+        <v>0.1543554982591644</v>
       </c>
       <c r="T48">
-        <v>2.021123286603988</v>
+        <v>2.059257688238025</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01879510719839687</v>
+        <v>0.01839521130055864</v>
       </c>
       <c r="W48">
-        <v>0.231368113722618</v>
+        <v>0.2314624091753283</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1253007146559791</v>
+        <v>0.1226347420037243</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1905957463897615</v>
+        <v>0.1924957463897615</v>
       </c>
       <c r="C49">
-        <v>-76.97841486599748</v>
+        <v>-96.64187158232801</v>
       </c>
       <c r="D49">
-        <v>509.8415851340026</v>
+        <v>503.2381284176719</v>
       </c>
       <c r="E49">
-        <v>522.62</v>
+        <v>535.6799999999999</v>
       </c>
       <c r="F49">
-        <v>613.8200000000001</v>
+        <v>626.88</v>
       </c>
       <c r="G49">
         <v>27</v>
@@ -5305,37 +5305,37 @@
         <v>17.75</v>
       </c>
       <c r="M49">
-        <v>144.738756</v>
+        <v>147.818304</v>
       </c>
       <c r="N49">
-        <v>-126.988756</v>
+        <v>-130.068304</v>
       </c>
       <c r="O49">
-        <v>-19.0483134</v>
+        <v>-19.5102456</v>
       </c>
       <c r="P49">
-        <v>-107.9404426</v>
+        <v>-110.5580584</v>
       </c>
       <c r="Q49">
-        <v>-101.9404426</v>
+        <v>-104.5580584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1543554982591644</v>
+        <v>0.1564431039949176</v>
       </c>
       <c r="T49">
-        <v>2.059257688238025</v>
+        <v>2.098858797627218</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01839521130055864</v>
+        <v>0.018011977731797</v>
       </c>
       <c r="W49">
-        <v>0.2314624091753283</v>
+        <v>0.2315527756508423</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1226347420037243</v>
+        <v>0.1200798515453133</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1924957463897614</v>
+        <v>0.1943957463897614</v>
       </c>
       <c r="C50">
-        <v>-96.64187158232801</v>
+        <v>-116.1364598341721</v>
       </c>
       <c r="D50">
-        <v>503.238128417672</v>
+        <v>496.8035401658278</v>
       </c>
       <c r="E50">
-        <v>535.6799999999999</v>
+        <v>548.7399999999999</v>
       </c>
       <c r="F50">
-        <v>626.88</v>
+        <v>639.9399999999999</v>
       </c>
       <c r="G50">
         <v>27</v>
@@ -5387,37 +5387,37 @@
         <v>17.75</v>
       </c>
       <c r="M50">
-        <v>147.818304</v>
+        <v>150.897852</v>
       </c>
       <c r="N50">
-        <v>-130.068304</v>
+        <v>-133.147852</v>
       </c>
       <c r="O50">
-        <v>-19.5102456</v>
+        <v>-19.9721778</v>
       </c>
       <c r="P50">
-        <v>-110.5580584</v>
+        <v>-113.1756742</v>
       </c>
       <c r="Q50">
-        <v>-104.5580584</v>
+        <v>-107.1756742</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1564431039949176</v>
+        <v>0.1586125766222689</v>
       </c>
       <c r="T50">
-        <v>2.098858797627218</v>
+        <v>2.14001289169834</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.018011977731797</v>
+        <v>0.01764438634951543</v>
       </c>
       <c r="W50">
-        <v>0.2315527756508423</v>
+        <v>0.2316394536987842</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1200798515453133</v>
+        <v>0.1176292423301029</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1943957463897614</v>
+        <v>0.1962957463897614</v>
       </c>
       <c r="C51">
-        <v>-116.1364598341721</v>
+        <v>-135.4685754850057</v>
       </c>
       <c r="D51">
-        <v>496.8035401658278</v>
+        <v>490.5314245149944</v>
       </c>
       <c r="E51">
-        <v>548.7399999999999</v>
+        <v>561.8</v>
       </c>
       <c r="F51">
-        <v>639.9399999999999</v>
+        <v>653</v>
       </c>
       <c r="G51">
         <v>27</v>
@@ -5469,37 +5469,37 @@
         <v>17.75</v>
       </c>
       <c r="M51">
-        <v>150.897852</v>
+        <v>153.9774</v>
       </c>
       <c r="N51">
-        <v>-133.147852</v>
+        <v>-136.2274</v>
       </c>
       <c r="O51">
-        <v>-19.9721778</v>
+        <v>-20.43411</v>
       </c>
       <c r="P51">
-        <v>-113.1756742</v>
+        <v>-115.79329</v>
       </c>
       <c r="Q51">
-        <v>-107.1756742</v>
+        <v>-109.79329</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1586125766222689</v>
+        <v>0.1608688281547143</v>
       </c>
       <c r="T51">
-        <v>2.14001289169834</v>
+        <v>2.182813149532307</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01764438634951543</v>
+        <v>0.01729149862252512</v>
       </c>
       <c r="W51">
-        <v>0.2316394536987842</v>
+        <v>0.2317226646248086</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1176292423301029</v>
+        <v>0.1152766574835008</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1962957463897614</v>
+        <v>0.1981957463897615</v>
       </c>
       <c r="C52">
-        <v>-135.4685754850057</v>
+        <v>-154.6442954355797</v>
       </c>
       <c r="D52">
-        <v>490.5314245149944</v>
+        <v>484.4157045644203</v>
       </c>
       <c r="E52">
-        <v>561.8</v>
+        <v>574.86</v>
       </c>
       <c r="F52">
-        <v>653</v>
+        <v>666.0600000000001</v>
       </c>
       <c r="G52">
         <v>27</v>
@@ -5551,37 +5551,37 @@
         <v>17.75</v>
       </c>
       <c r="M52">
-        <v>153.9774</v>
+        <v>157.056948</v>
       </c>
       <c r="N52">
-        <v>-136.2274</v>
+        <v>-139.306948</v>
       </c>
       <c r="O52">
-        <v>-20.43411</v>
+        <v>-20.8960422</v>
       </c>
       <c r="P52">
-        <v>-115.79329</v>
+        <v>-118.4109058</v>
       </c>
       <c r="Q52">
-        <v>-109.79329</v>
+        <v>-112.4109058</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1608688281547143</v>
+        <v>0.1632171715864432</v>
       </c>
       <c r="T52">
-        <v>2.182813149532307</v>
+        <v>2.22736035666562</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01729149862252512</v>
+        <v>0.01695244962992659</v>
       </c>
       <c r="W52">
-        <v>0.2317226646248086</v>
+        <v>0.2318026123772633</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1152766574835008</v>
+        <v>0.1130163308661772</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1981957463897615</v>
+        <v>0.2000957463897615</v>
       </c>
       <c r="C53">
-        <v>-154.6442954355797</v>
+        <v>-173.6693972624792</v>
       </c>
       <c r="D53">
-        <v>484.4157045644203</v>
+        <v>478.4506027375208</v>
       </c>
       <c r="E53">
-        <v>574.86</v>
+        <v>587.92</v>
       </c>
       <c r="F53">
-        <v>666.0600000000001</v>
+        <v>679.12</v>
       </c>
       <c r="G53">
         <v>27</v>
@@ -5633,37 +5633,37 @@
         <v>17.75</v>
       </c>
       <c r="M53">
-        <v>157.056948</v>
+        <v>160.136496</v>
       </c>
       <c r="N53">
-        <v>-139.306948</v>
+        <v>-142.386496</v>
       </c>
       <c r="O53">
-        <v>-20.8960422</v>
+        <v>-21.3579744</v>
       </c>
       <c r="P53">
-        <v>-118.4109058</v>
+        <v>-121.0285216</v>
       </c>
       <c r="Q53">
-        <v>-112.4109058</v>
+        <v>-115.0285216</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1632171715864432</v>
+        <v>0.1656633626611607</v>
       </c>
       <c r="T53">
-        <v>2.22736035666562</v>
+        <v>2.273763697429487</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01695244962992659</v>
+        <v>0.01662644098319723</v>
       </c>
       <c r="W53">
-        <v>0.2318026123772633</v>
+        <v>0.2318794852161621</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1130163308661772</v>
+        <v>0.1108429398879816</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2000957463897615</v>
+        <v>0.2019957463897615</v>
       </c>
       <c r="C54">
-        <v>-173.6693972624792</v>
+        <v>-192.5493774233531</v>
       </c>
       <c r="D54">
-        <v>478.4506027375208</v>
+        <v>472.6306225766469</v>
       </c>
       <c r="E54">
-        <v>587.92</v>
+        <v>600.98</v>
       </c>
       <c r="F54">
-        <v>679.12</v>
+        <v>692.1800000000001</v>
       </c>
       <c r="G54">
         <v>27</v>
@@ -5715,37 +5715,37 @@
         <v>17.75</v>
       </c>
       <c r="M54">
-        <v>160.136496</v>
+        <v>163.216044</v>
       </c>
       <c r="N54">
-        <v>-142.386496</v>
+        <v>-145.466044</v>
       </c>
       <c r="O54">
-        <v>-21.3579744</v>
+        <v>-21.8199066</v>
       </c>
       <c r="P54">
-        <v>-121.0285216</v>
+        <v>-123.6461374</v>
       </c>
       <c r="Q54">
-        <v>-115.0285216</v>
+        <v>-117.6461374</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1656633626611607</v>
+        <v>0.1682136469731003</v>
       </c>
       <c r="T54">
-        <v>2.273763697429487</v>
+        <v>2.322141648438625</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01662644098319723</v>
+        <v>0.016312734549552</v>
       </c>
       <c r="W54">
-        <v>0.2318794852161621</v>
+        <v>0.2319534571932157</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1108429398879816</v>
+        <v>0.10875156366368</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2019957463897615</v>
+        <v>0.2038957463897614</v>
       </c>
       <c r="C55">
-        <v>-192.5493774233531</v>
+        <v>-211.2894681493979</v>
       </c>
       <c r="D55">
-        <v>472.6306225766469</v>
+        <v>466.9505318506021</v>
       </c>
       <c r="E55">
-        <v>600.98</v>
+        <v>614.04</v>
       </c>
       <c r="F55">
-        <v>692.1800000000001</v>
+        <v>705.24</v>
       </c>
       <c r="G55">
         <v>27</v>
@@ -5797,37 +5797,37 @@
         <v>17.75</v>
       </c>
       <c r="M55">
-        <v>163.216044</v>
+        <v>166.295592</v>
       </c>
       <c r="N55">
-        <v>-145.466044</v>
+        <v>-148.545592</v>
       </c>
       <c r="O55">
-        <v>-21.8199066</v>
+        <v>-22.2818388</v>
       </c>
       <c r="P55">
-        <v>-123.6461374</v>
+        <v>-126.2637532</v>
       </c>
       <c r="Q55">
-        <v>-117.6461374</v>
+        <v>-120.2637532</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1682136469731003</v>
+        <v>0.170874813211646</v>
       </c>
       <c r="T55">
-        <v>2.322141648438625</v>
+        <v>2.372622988622073</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.016312734549552</v>
+        <v>0.01601064687270845</v>
       </c>
       <c r="W55">
-        <v>0.2319534571932157</v>
+        <v>0.2320246894674154</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.10875156366368</v>
+        <v>0.1067376458180563</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2038957463897614</v>
+        <v>0.2057957463897614</v>
       </c>
       <c r="C56">
-        <v>-211.2894681493979</v>
+        <v>-229.8946531342215</v>
       </c>
       <c r="D56">
-        <v>466.9505318506021</v>
+        <v>461.4053468657785</v>
       </c>
       <c r="E56">
-        <v>614.04</v>
+        <v>627.1</v>
       </c>
       <c r="F56">
-        <v>705.24</v>
+        <v>718.3000000000001</v>
       </c>
       <c r="G56">
         <v>27</v>
@@ -5879,37 +5879,37 @@
         <v>17.75</v>
       </c>
       <c r="M56">
-        <v>166.295592</v>
+        <v>169.37514</v>
       </c>
       <c r="N56">
-        <v>-148.545592</v>
+        <v>-151.62514</v>
       </c>
       <c r="O56">
-        <v>-22.2818388</v>
+        <v>-22.743771</v>
       </c>
       <c r="P56">
-        <v>-126.2637532</v>
+        <v>-128.881369</v>
       </c>
       <c r="Q56">
-        <v>-120.2637532</v>
+        <v>-122.881369</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.170874813211646</v>
+        <v>0.1736542535052381</v>
       </c>
       <c r="T56">
-        <v>2.372622988622073</v>
+        <v>2.425347943924786</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01601064687270845</v>
+        <v>0.01571954420229556</v>
       </c>
       <c r="W56">
-        <v>0.2320246894674154</v>
+        <v>0.2320933314770987</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1067376458180563</v>
+        <v>0.1047969613486371</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2057957463897614</v>
+        <v>0.2076957463897615</v>
       </c>
       <c r="C57">
-        <v>-229.8946531342215</v>
+        <v>-248.3696821179627</v>
       </c>
       <c r="D57">
-        <v>461.4053468657785</v>
+        <v>455.9903178820373</v>
       </c>
       <c r="E57">
-        <v>627.1</v>
+        <v>640.16</v>
       </c>
       <c r="F57">
-        <v>718.3000000000001</v>
+        <v>731.36</v>
       </c>
       <c r="G57">
         <v>27</v>
@@ -5961,37 +5961,37 @@
         <v>17.75</v>
       </c>
       <c r="M57">
-        <v>169.37514</v>
+        <v>172.454688</v>
       </c>
       <c r="N57">
-        <v>-151.62514</v>
+        <v>-154.704688</v>
       </c>
       <c r="O57">
-        <v>-22.743771</v>
+        <v>-23.2057032</v>
       </c>
       <c r="P57">
-        <v>-128.881369</v>
+        <v>-131.4989848</v>
       </c>
       <c r="Q57">
-        <v>-122.881369</v>
+        <v>-125.4989848</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1736542535052381</v>
+        <v>0.1765600319939935</v>
       </c>
       <c r="T57">
-        <v>2.425347943924786</v>
+        <v>2.480469488104894</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01571954420229556</v>
+        <v>0.015438838055826</v>
       </c>
       <c r="W57">
-        <v>0.2320933314770987</v>
+        <v>0.2321595219864362</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1047969613486371</v>
+        <v>0.10292558703884</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2076957463897615</v>
+        <v>0.2095957463897614</v>
       </c>
       <c r="C58">
-        <v>-248.3696821179627</v>
+        <v>-266.7190844563743</v>
       </c>
       <c r="D58">
-        <v>455.9903178820373</v>
+        <v>450.7009155436258</v>
       </c>
       <c r="E58">
-        <v>640.16</v>
+        <v>653.22</v>
       </c>
       <c r="F58">
-        <v>731.36</v>
+        <v>744.4200000000001</v>
       </c>
       <c r="G58">
         <v>27</v>
@@ -6043,37 +6043,37 @@
         <v>17.75</v>
       </c>
       <c r="M58">
-        <v>172.454688</v>
+        <v>175.534236</v>
       </c>
       <c r="N58">
-        <v>-154.704688</v>
+        <v>-157.784236</v>
       </c>
       <c r="O58">
-        <v>-23.2057032</v>
+        <v>-23.6676354</v>
       </c>
       <c r="P58">
-        <v>-131.4989848</v>
+        <v>-134.1166006</v>
       </c>
       <c r="Q58">
-        <v>-125.4989848</v>
+        <v>-128.1166006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1765600319939935</v>
+        <v>0.179600962970598</v>
       </c>
       <c r="T58">
-        <v>2.480469488104894</v>
+        <v>2.538154825037567</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.015438838055826</v>
+        <v>0.01516798124782905</v>
       </c>
       <c r="W58">
-        <v>0.2321595219864362</v>
+        <v>0.2322233900217619</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.10292558703884</v>
+        <v>0.101119874985527</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2095957463897614</v>
+        <v>0.2114957463897614</v>
       </c>
       <c r="C59">
-        <v>-266.7190844563743</v>
+        <v>-284.947181756341</v>
       </c>
       <c r="D59">
-        <v>450.7009155436258</v>
+        <v>445.5328182436591</v>
       </c>
       <c r="E59">
-        <v>653.22</v>
+        <v>666.2800000000001</v>
       </c>
       <c r="F59">
-        <v>744.4200000000001</v>
+        <v>757.4800000000001</v>
       </c>
       <c r="G59">
         <v>27</v>
@@ -6125,37 +6125,37 @@
         <v>17.75</v>
       </c>
       <c r="M59">
-        <v>175.534236</v>
+        <v>178.613784</v>
       </c>
       <c r="N59">
-        <v>-157.784236</v>
+        <v>-160.863784</v>
       </c>
       <c r="O59">
-        <v>-23.6676354</v>
+        <v>-24.12956760000001</v>
       </c>
       <c r="P59">
-        <v>-134.1166006</v>
+        <v>-136.7342164</v>
       </c>
       <c r="Q59">
-        <v>-128.1166006</v>
+        <v>-130.7342164</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.179600962970598</v>
+        <v>0.1827867001841837</v>
       </c>
       <c r="T59">
-        <v>2.538154825037567</v>
+        <v>2.598587082776556</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01516798124782905</v>
+        <v>0.01490646432976303</v>
       </c>
       <c r="W59">
-        <v>0.2322233900217619</v>
+        <v>0.2322850557110419</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.101119874985527</v>
+        <v>0.09937642886508691</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2114957463897614</v>
+        <v>0.2133957463897614</v>
       </c>
       <c r="C60">
-        <v>-284.9471817563408</v>
+        <v>-303.0580996519198</v>
       </c>
       <c r="D60">
-        <v>445.5328182436591</v>
+        <v>440.4819003480802</v>
       </c>
       <c r="E60">
-        <v>666.2799999999999</v>
+        <v>679.3399999999999</v>
       </c>
       <c r="F60">
-        <v>757.4799999999999</v>
+        <v>770.54</v>
       </c>
       <c r="G60">
         <v>27</v>
@@ -6207,37 +6207,37 @@
         <v>17.75</v>
       </c>
       <c r="M60">
-        <v>178.613784</v>
+        <v>181.693332</v>
       </c>
       <c r="N60">
-        <v>-160.863784</v>
+        <v>-163.943332</v>
       </c>
       <c r="O60">
-        <v>-24.1295676</v>
+        <v>-24.5914998</v>
       </c>
       <c r="P60">
-        <v>-136.7342164</v>
+        <v>-139.3518322</v>
       </c>
       <c r="Q60">
-        <v>-130.7342164</v>
+        <v>-133.3518322</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1827867001841837</v>
+        <v>0.1861278392130662</v>
       </c>
       <c r="T60">
-        <v>2.598587082776556</v>
+        <v>2.661967255527203</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01490646432976304</v>
+        <v>0.01465381239197044</v>
       </c>
       <c r="W60">
-        <v>0.2322850557110419</v>
+        <v>0.2323446310379734</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09937642886508691</v>
+        <v>0.09769208261313633</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2133957463897614</v>
+        <v>0.2152957463897614</v>
       </c>
       <c r="C61">
-        <v>-303.0580996519198</v>
+        <v>-321.0557787883438</v>
       </c>
       <c r="D61">
-        <v>440.4819003480802</v>
+        <v>435.5442212116562</v>
       </c>
       <c r="E61">
-        <v>679.3399999999999</v>
+        <v>692.4</v>
       </c>
       <c r="F61">
-        <v>770.54</v>
+        <v>783.6</v>
       </c>
       <c r="G61">
         <v>27</v>
@@ -6289,37 +6289,37 @@
         <v>17.75</v>
       </c>
       <c r="M61">
-        <v>181.693332</v>
+        <v>184.77288</v>
       </c>
       <c r="N61">
-        <v>-163.943332</v>
+        <v>-167.02288</v>
       </c>
       <c r="O61">
-        <v>-24.5914998</v>
+        <v>-25.053432</v>
       </c>
       <c r="P61">
-        <v>-139.3518322</v>
+        <v>-141.969448</v>
       </c>
       <c r="Q61">
-        <v>-133.3518322</v>
+        <v>-135.969448</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1861278392130662</v>
+        <v>0.1896360351933929</v>
       </c>
       <c r="T61">
-        <v>2.661967255527203</v>
+        <v>2.728516436915384</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01465381239197044</v>
+        <v>0.0144095821854376</v>
       </c>
       <c r="W61">
-        <v>0.2323446310379734</v>
+        <v>0.2324022205206738</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09769208261313633</v>
+        <v>0.09606388123625065</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2152957463897614</v>
+        <v>0.2171957463897614</v>
       </c>
       <c r="C62">
-        <v>-321.0557787883438</v>
+        <v>-338.9439850754492</v>
       </c>
       <c r="D62">
-        <v>435.5442212116562</v>
+        <v>430.7160149245508</v>
       </c>
       <c r="E62">
-        <v>692.4</v>
+        <v>705.4599999999999</v>
       </c>
       <c r="F62">
-        <v>783.6</v>
+        <v>796.66</v>
       </c>
       <c r="G62">
         <v>27</v>
@@ -6371,37 +6371,37 @@
         <v>17.75</v>
       </c>
       <c r="M62">
-        <v>184.77288</v>
+        <v>187.852428</v>
       </c>
       <c r="N62">
-        <v>-167.02288</v>
+        <v>-170.102428</v>
       </c>
       <c r="O62">
-        <v>-25.053432</v>
+        <v>-25.5153642</v>
       </c>
       <c r="P62">
-        <v>-141.969448</v>
+        <v>-144.5870638</v>
       </c>
       <c r="Q62">
-        <v>-135.969448</v>
+        <v>-138.5870638</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1896360351933929</v>
+        <v>0.1933241386598901</v>
       </c>
       <c r="T62">
-        <v>2.728516436915384</v>
+        <v>2.798478396836291</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0144095821854376</v>
+        <v>0.01417335952665994</v>
       </c>
       <c r="W62">
-        <v>0.2324022205206738</v>
+        <v>0.2324579218236136</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09606388123625065</v>
+        <v>0.09448906351106623</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2171957463897614</v>
+        <v>0.2190957463897615</v>
       </c>
       <c r="C63">
-        <v>-338.9439850754492</v>
+        <v>-356.7263192665959</v>
       </c>
       <c r="D63">
-        <v>430.7160149245508</v>
+        <v>425.9936807334042</v>
       </c>
       <c r="E63">
-        <v>705.4599999999999</v>
+        <v>718.52</v>
       </c>
       <c r="F63">
-        <v>796.66</v>
+        <v>809.72</v>
       </c>
       <c r="G63">
         <v>27</v>
@@ -6453,37 +6453,37 @@
         <v>17.75</v>
       </c>
       <c r="M63">
-        <v>187.852428</v>
+        <v>190.931976</v>
       </c>
       <c r="N63">
-        <v>-170.102428</v>
+        <v>-173.181976</v>
       </c>
       <c r="O63">
-        <v>-25.5153642</v>
+        <v>-25.9772964</v>
       </c>
       <c r="P63">
-        <v>-144.5870638</v>
+        <v>-147.2046796</v>
       </c>
       <c r="Q63">
-        <v>-138.5870638</v>
+        <v>-141.2046796</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1933241386598901</v>
+        <v>0.1972063528351504</v>
       </c>
       <c r="T63">
-        <v>2.798478396836291</v>
+        <v>2.872122565174088</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01417335952665994</v>
+        <v>0.01394475695364929</v>
       </c>
       <c r="W63">
-        <v>0.2324579218236136</v>
+        <v>0.2325118263103295</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09448906351106623</v>
+        <v>0.0929650463576619</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2190957463897615</v>
+        <v>0.2209957463897614</v>
       </c>
       <c r="C64">
-        <v>-356.7263192665959</v>
+        <v>-374.4062259142881</v>
       </c>
       <c r="D64">
-        <v>425.9936807334042</v>
+        <v>421.3737740857118</v>
       </c>
       <c r="E64">
-        <v>718.52</v>
+        <v>731.5799999999999</v>
       </c>
       <c r="F64">
-        <v>809.72</v>
+        <v>822.78</v>
       </c>
       <c r="G64">
         <v>27</v>
@@ -6535,37 +6535,37 @@
         <v>17.75</v>
       </c>
       <c r="M64">
-        <v>190.931976</v>
+        <v>194.011524</v>
       </c>
       <c r="N64">
-        <v>-173.181976</v>
+        <v>-176.261524</v>
       </c>
       <c r="O64">
-        <v>-25.9772964</v>
+        <v>-26.4392286</v>
       </c>
       <c r="P64">
-        <v>-147.2046796</v>
+        <v>-149.8222954</v>
       </c>
       <c r="Q64">
-        <v>-141.2046796</v>
+        <v>-143.8222954</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1972063528351504</v>
+        <v>0.2012984164252896</v>
       </c>
       <c r="T64">
-        <v>2.872122565174088</v>
+        <v>2.949747499367982</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01394475695364929</v>
+        <v>0.01372341160517867</v>
       </c>
       <c r="W64">
-        <v>0.2325118263103295</v>
+        <v>0.2325640195434989</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0929650463576619</v>
+        <v>0.0914894107011911</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2209957463897614</v>
+        <v>0.2228957463897615</v>
       </c>
       <c r="C65">
-        <v>-374.4062259142881</v>
+        <v>-391.9870017493036</v>
       </c>
       <c r="D65">
-        <v>421.3737740857118</v>
+        <v>416.8529982506964</v>
       </c>
       <c r="E65">
-        <v>731.5799999999999</v>
+        <v>744.64</v>
       </c>
       <c r="F65">
-        <v>822.78</v>
+        <v>835.84</v>
       </c>
       <c r="G65">
         <v>27</v>
@@ -6617,37 +6617,37 @@
         <v>17.75</v>
       </c>
       <c r="M65">
-        <v>194.011524</v>
+        <v>197.091072</v>
       </c>
       <c r="N65">
-        <v>-176.261524</v>
+        <v>-179.341072</v>
       </c>
       <c r="O65">
-        <v>-26.4392286</v>
+        <v>-26.9011608</v>
       </c>
       <c r="P65">
-        <v>-149.8222954</v>
+        <v>-152.4399112</v>
       </c>
       <c r="Q65">
-        <v>-143.8222954</v>
+        <v>-146.4399112</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2012984164252896</v>
+        <v>0.2056178168815476</v>
       </c>
       <c r="T65">
-        <v>2.949747499367982</v>
+        <v>3.031684929905982</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01372341160517867</v>
+        <v>0.01350898329884775</v>
       </c>
       <c r="W65">
-        <v>0.2325640195434989</v>
+        <v>0.2326145817381317</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.0914894107011911</v>
+        <v>0.09005988865898495</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2228957463897615</v>
+        <v>0.2247957463897615</v>
       </c>
       <c r="C66">
-        <v>-391.9870017493036</v>
+        <v>-409.4718035261665</v>
       </c>
       <c r="D66">
-        <v>416.8529982506964</v>
+        <v>412.4281964738335</v>
       </c>
       <c r="E66">
-        <v>744.64</v>
+        <v>757.6999999999999</v>
       </c>
       <c r="F66">
-        <v>835.84</v>
+        <v>848.9</v>
       </c>
       <c r="G66">
         <v>27</v>
@@ -6699,37 +6699,37 @@
         <v>17.75</v>
       </c>
       <c r="M66">
-        <v>197.091072</v>
+        <v>200.17062</v>
       </c>
       <c r="N66">
-        <v>-179.341072</v>
+        <v>-182.42062</v>
       </c>
       <c r="O66">
-        <v>-26.9011608</v>
+        <v>-27.363093</v>
       </c>
       <c r="P66">
-        <v>-152.4399112</v>
+        <v>-155.057527</v>
       </c>
       <c r="Q66">
-        <v>-146.4399112</v>
+        <v>-149.057527</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2056178168815476</v>
+        <v>0.2101840402210204</v>
       </c>
       <c r="T66">
-        <v>3.031684929905982</v>
+        <v>3.118304499331867</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01350898329884775</v>
+        <v>0.01330115278655779</v>
       </c>
       <c r="W66">
-        <v>0.2326145817381317</v>
+        <v>0.2326635881729297</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09005988865898495</v>
+        <v>0.0886743519103852</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2247957463897615</v>
+        <v>0.2266957463897614</v>
       </c>
       <c r="C67">
-        <v>-409.4718035261665</v>
+        <v>-426.8636553742022</v>
       </c>
       <c r="D67">
-        <v>412.4281964738335</v>
+        <v>408.0963446257979</v>
       </c>
       <c r="E67">
-        <v>757.6999999999999</v>
+        <v>770.76</v>
       </c>
       <c r="F67">
-        <v>848.9</v>
+        <v>861.96</v>
       </c>
       <c r="G67">
         <v>27</v>
@@ -6781,37 +6781,37 @@
         <v>17.75</v>
       </c>
       <c r="M67">
-        <v>200.17062</v>
+        <v>203.250168</v>
       </c>
       <c r="N67">
-        <v>-182.42062</v>
+        <v>-185.500168</v>
       </c>
       <c r="O67">
-        <v>-27.363093</v>
+        <v>-27.8250252</v>
       </c>
       <c r="P67">
-        <v>-155.057527</v>
+        <v>-157.6751428</v>
       </c>
       <c r="Q67">
-        <v>-149.057527</v>
+        <v>-151.6751428</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2101840402210204</v>
+        <v>0.2150188649334034</v>
       </c>
       <c r="T67">
-        <v>3.118304499331867</v>
+        <v>3.21001933754751</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01330115278655779</v>
+        <v>0.01309962016857964</v>
       </c>
       <c r="W67">
-        <v>0.2326635881729297</v>
+        <v>0.2327111095642489</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0886743519103852</v>
+        <v>0.08733080112386427</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2266957463897614</v>
+        <v>0.2285957463897614</v>
       </c>
       <c r="C68">
-        <v>-426.8636553742022</v>
+        <v>-444.1654556901446</v>
       </c>
       <c r="D68">
-        <v>408.0963446257979</v>
+        <v>403.8545443098555</v>
       </c>
       <c r="E68">
-        <v>770.76</v>
+        <v>783.8200000000001</v>
       </c>
       <c r="F68">
-        <v>861.96</v>
+        <v>875.0200000000001</v>
       </c>
       <c r="G68">
         <v>27</v>
@@ -6863,37 +6863,37 @@
         <v>17.75</v>
       </c>
       <c r="M68">
-        <v>203.250168</v>
+        <v>206.329716</v>
       </c>
       <c r="N68">
-        <v>-185.500168</v>
+        <v>-188.579716</v>
       </c>
       <c r="O68">
-        <v>-27.8250252</v>
+        <v>-28.2869574</v>
       </c>
       <c r="P68">
-        <v>-157.6751428</v>
+        <v>-160.2927586</v>
       </c>
       <c r="Q68">
-        <v>-151.6751428</v>
+        <v>-154.2927586</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2150188649334034</v>
+        <v>0.2201467093253247</v>
       </c>
       <c r="T68">
-        <v>3.21001933754751</v>
+        <v>3.307292650806526</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01309962016857964</v>
+        <v>0.01290410344964561</v>
       </c>
       <c r="W68">
-        <v>0.2327111095642489</v>
+        <v>0.2327572124065736</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08733080112386427</v>
+        <v>0.08602735633097081</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2285957463897614</v>
+        <v>0.2304957463897614</v>
       </c>
       <c r="C69">
-        <v>-444.1654556901446</v>
+        <v>-461.3799836053109</v>
       </c>
       <c r="D69">
-        <v>403.8545443098555</v>
+        <v>399.7000163946892</v>
       </c>
       <c r="E69">
-        <v>783.8200000000001</v>
+        <v>796.88</v>
       </c>
       <c r="F69">
-        <v>875.0200000000001</v>
+        <v>888.08</v>
       </c>
       <c r="G69">
         <v>27</v>
@@ -6945,37 +6945,37 @@
         <v>17.75</v>
       </c>
       <c r="M69">
-        <v>206.329716</v>
+        <v>209.409264</v>
       </c>
       <c r="N69">
-        <v>-188.579716</v>
+        <v>-191.659264</v>
       </c>
       <c r="O69">
-        <v>-28.2869574</v>
+        <v>-28.7488896</v>
       </c>
       <c r="P69">
-        <v>-160.2927586</v>
+        <v>-162.9103744</v>
       </c>
       <c r="Q69">
-        <v>-154.2927586</v>
+        <v>-156.9103744</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2201467093253247</v>
+        <v>0.2255950439917411</v>
       </c>
       <c r="T69">
-        <v>3.307292650806526</v>
+        <v>3.41064554614423</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01290410344964561</v>
+        <v>0.01271433722244494</v>
       </c>
       <c r="W69">
-        <v>0.2327572124065736</v>
+        <v>0.2328019592829475</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08602735633097081</v>
+        <v>0.08476224814963296</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2304957463897614</v>
+        <v>0.2323957463897614</v>
       </c>
       <c r="C70">
-        <v>-461.3799836053109</v>
+        <v>-478.5099050576661</v>
       </c>
       <c r="D70">
-        <v>399.7000163946892</v>
+        <v>395.630094942334</v>
       </c>
       <c r="E70">
-        <v>796.88</v>
+        <v>809.9400000000001</v>
       </c>
       <c r="F70">
-        <v>888.08</v>
+        <v>901.1400000000001</v>
       </c>
       <c r="G70">
         <v>27</v>
@@ -7027,37 +7027,37 @@
         <v>17.75</v>
       </c>
       <c r="M70">
-        <v>209.409264</v>
+        <v>212.488812</v>
       </c>
       <c r="N70">
-        <v>-191.659264</v>
+        <v>-194.738812</v>
       </c>
       <c r="O70">
-        <v>-28.7488896</v>
+        <v>-29.2108218</v>
       </c>
       <c r="P70">
-        <v>-162.9103744</v>
+        <v>-165.5279902</v>
       </c>
       <c r="Q70">
-        <v>-156.9103744</v>
+        <v>-159.5279902</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2255950439917411</v>
+        <v>0.231394884120507</v>
       </c>
       <c r="T70">
-        <v>3.41064554614423</v>
+        <v>3.520666370213399</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01271433722244494</v>
+        <v>0.01253007146559791</v>
       </c>
       <c r="W70">
-        <v>0.2328019592829475</v>
+        <v>0.232845409148412</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08476224814963296</v>
+        <v>0.08353380977065272</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2323957463897614</v>
+        <v>0.2342957463897615</v>
       </c>
       <c r="C71">
-        <v>-478.5099050576661</v>
+        <v>-495.5577784966566</v>
       </c>
       <c r="D71">
-        <v>395.630094942334</v>
+        <v>391.6422215033435</v>
       </c>
       <c r="E71">
-        <v>809.9400000000001</v>
+        <v>823</v>
       </c>
       <c r="F71">
-        <v>901.1400000000001</v>
+        <v>914.2</v>
       </c>
       <c r="G71">
         <v>27</v>
@@ -7109,37 +7109,37 @@
         <v>17.75</v>
       </c>
       <c r="M71">
-        <v>212.488812</v>
+        <v>215.56836</v>
       </c>
       <c r="N71">
-        <v>-194.738812</v>
+        <v>-197.81836</v>
       </c>
       <c r="O71">
-        <v>-29.2108218</v>
+        <v>-29.672754</v>
       </c>
       <c r="P71">
-        <v>-165.5279902</v>
+        <v>-168.145606</v>
       </c>
       <c r="Q71">
-        <v>-159.5279902</v>
+        <v>-162.145606</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.231394884120507</v>
+        <v>0.2375813802578572</v>
       </c>
       <c r="T71">
-        <v>3.520666370213399</v>
+        <v>3.638021915887179</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01253007146559791</v>
+        <v>0.0123510704446608</v>
       </c>
       <c r="W71">
-        <v>0.232845409148412</v>
+        <v>0.232887617589149</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08353380977065272</v>
+        <v>0.082340469631072</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2342957463897615</v>
+        <v>0.2361957463897615</v>
       </c>
       <c r="C72">
-        <v>-495.5577784966566</v>
+        <v>-512.5260602464656</v>
       </c>
       <c r="D72">
-        <v>391.6422215033435</v>
+        <v>387.7339397535345</v>
       </c>
       <c r="E72">
-        <v>823</v>
+        <v>836.0600000000001</v>
       </c>
       <c r="F72">
-        <v>914.2</v>
+        <v>927.2600000000001</v>
       </c>
       <c r="G72">
         <v>27</v>
@@ -7191,37 +7191,37 @@
         <v>17.75</v>
       </c>
       <c r="M72">
-        <v>215.56836</v>
+        <v>218.647908</v>
       </c>
       <c r="N72">
-        <v>-197.81836</v>
+        <v>-200.897908</v>
       </c>
       <c r="O72">
-        <v>-29.672754</v>
+        <v>-30.1346862</v>
       </c>
       <c r="P72">
-        <v>-168.145606</v>
+        <v>-170.7632218</v>
       </c>
       <c r="Q72">
-        <v>-162.145606</v>
+        <v>-164.7632218</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2375813802578572</v>
+        <v>0.2441945313012316</v>
       </c>
       <c r="T72">
-        <v>3.638021915887179</v>
+        <v>3.763470947469496</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0123510704446608</v>
+        <v>0.01217711170600361</v>
       </c>
       <c r="W72">
-        <v>0.232887617589149</v>
+        <v>0.2329286370597244</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.082340469631072</v>
+        <v>0.08118074470669068</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2361957463897614</v>
+        <v>0.2380957463897614</v>
       </c>
       <c r="C73">
-        <v>-512.5260602464652</v>
+        <v>-529.4171095513134</v>
       </c>
       <c r="D73">
-        <v>387.7339397535347</v>
+        <v>383.9028904486866</v>
       </c>
       <c r="E73">
-        <v>836.0599999999999</v>
+        <v>849.1199999999999</v>
       </c>
       <c r="F73">
-        <v>927.26</v>
+        <v>940.3199999999999</v>
       </c>
       <c r="G73">
         <v>27</v>
@@ -7273,37 +7273,37 @@
         <v>17.75</v>
       </c>
       <c r="M73">
-        <v>218.647908</v>
+        <v>221.727456</v>
       </c>
       <c r="N73">
-        <v>-200.897908</v>
+        <v>-203.977456</v>
       </c>
       <c r="O73">
-        <v>-30.1346862</v>
+        <v>-30.5966184</v>
       </c>
       <c r="P73">
-        <v>-170.7632218</v>
+        <v>-173.3808376</v>
       </c>
       <c r="Q73">
-        <v>-164.7632218</v>
+        <v>-167.3808376</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2441945313012315</v>
+        <v>0.2512800502762755</v>
       </c>
       <c r="T73">
-        <v>3.763470947469494</v>
+        <v>3.897880624164833</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01217711170600361</v>
+        <v>0.01200798515453134</v>
       </c>
       <c r="W73">
-        <v>0.2329286370597244</v>
+        <v>0.2329685171005615</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08118074470669068</v>
+        <v>0.08005323436354228</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2380957463897614</v>
+        <v>0.2399957463897614</v>
       </c>
       <c r="C74">
-        <v>-529.4171095513134</v>
+        <v>-546.2331933245827</v>
       </c>
       <c r="D74">
-        <v>383.9028904486866</v>
+        <v>380.1468066754173</v>
       </c>
       <c r="E74">
-        <v>849.1199999999999</v>
+        <v>862.1799999999999</v>
       </c>
       <c r="F74">
-        <v>940.3199999999999</v>
+        <v>953.38</v>
       </c>
       <c r="G74">
         <v>27</v>
@@ -7355,37 +7355,37 @@
         <v>17.75</v>
       </c>
       <c r="M74">
-        <v>221.727456</v>
+        <v>224.807004</v>
       </c>
       <c r="N74">
-        <v>-203.977456</v>
+        <v>-207.057004</v>
       </c>
       <c r="O74">
-        <v>-30.5966184</v>
+        <v>-31.0585506</v>
       </c>
       <c r="P74">
-        <v>-173.3808376</v>
+        <v>-175.9984534</v>
       </c>
       <c r="Q74">
-        <v>-167.3808376</v>
+        <v>-169.9984534</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2512800502762755</v>
+        <v>0.2588904225087301</v>
       </c>
       <c r="T74">
-        <v>3.897880624164833</v>
+        <v>4.042246573207975</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01200798515453134</v>
+        <v>0.01184349220720899</v>
       </c>
       <c r="W74">
-        <v>0.2329685171005615</v>
+        <v>0.2330073045375401</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08005323436354228</v>
+        <v>0.07895661471472659</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2399957463897614</v>
+        <v>0.2418957463897614</v>
       </c>
       <c r="C75">
-        <v>-546.2331933245827</v>
+        <v>-562.9764906218513</v>
       </c>
       <c r="D75">
-        <v>380.1468066754173</v>
+        <v>376.4635093781486</v>
       </c>
       <c r="E75">
-        <v>862.1799999999999</v>
+        <v>875.2399999999999</v>
       </c>
       <c r="F75">
-        <v>953.38</v>
+        <v>966.4399999999999</v>
       </c>
       <c r="G75">
         <v>27</v>
@@ -7437,37 +7437,37 @@
         <v>17.75</v>
       </c>
       <c r="M75">
-        <v>224.807004</v>
+        <v>227.886552</v>
       </c>
       <c r="N75">
-        <v>-207.057004</v>
+        <v>-210.136552</v>
       </c>
       <c r="O75">
-        <v>-31.0585506</v>
+        <v>-31.5204828</v>
       </c>
       <c r="P75">
-        <v>-175.9984534</v>
+        <v>-178.6160692</v>
       </c>
       <c r="Q75">
-        <v>-169.9984534</v>
+        <v>-172.6160692</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2588904225087301</v>
+        <v>0.2670862079898352</v>
       </c>
       <c r="T75">
-        <v>4.042246573207975</v>
+        <v>4.197717595254436</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01184349220720899</v>
+        <v>0.01168344501521968</v>
       </c>
       <c r="W75">
-        <v>0.2330073045375401</v>
+        <v>0.2330450436654112</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07895661471472659</v>
+        <v>0.07788963343479782</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2418957463897614</v>
+        <v>0.2437957463897615</v>
       </c>
       <c r="C76">
-        <v>-562.9764906218513</v>
+        <v>-579.6490968563835</v>
       </c>
       <c r="D76">
-        <v>376.4635093781486</v>
+        <v>372.8509031436164</v>
       </c>
       <c r="E76">
-        <v>875.2399999999999</v>
+        <v>888.3</v>
       </c>
       <c r="F76">
-        <v>966.4399999999999</v>
+        <v>979.5</v>
       </c>
       <c r="G76">
         <v>27</v>
@@ -7519,37 +7519,37 @@
         <v>17.75</v>
       </c>
       <c r="M76">
-        <v>227.886552</v>
+        <v>230.9661</v>
       </c>
       <c r="N76">
-        <v>-210.136552</v>
+        <v>-213.2161</v>
       </c>
       <c r="O76">
-        <v>-31.5204828</v>
+        <v>-31.982415</v>
       </c>
       <c r="P76">
-        <v>-178.6160692</v>
+        <v>-181.233685</v>
       </c>
       <c r="Q76">
-        <v>-172.6160692</v>
+        <v>-175.233685</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2670862079898352</v>
+        <v>0.2759376563094286</v>
       </c>
       <c r="T76">
-        <v>4.197717595254436</v>
+        <v>4.365626299064614</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01168344501521968</v>
+        <v>0.01152766574835008</v>
       </c>
       <c r="W76">
-        <v>0.2330450436654112</v>
+        <v>0.2330817764165391</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07788963343479782</v>
+        <v>0.0768511049890005</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2437957463897615</v>
+        <v>0.2456957463897615</v>
       </c>
       <c r="C77">
-        <v>-579.6490968563835</v>
+        <v>-596.253027774211</v>
       </c>
       <c r="D77">
-        <v>372.8509031436164</v>
+        <v>369.3069722257891</v>
       </c>
       <c r="E77">
-        <v>888.3</v>
+        <v>901.36</v>
       </c>
       <c r="F77">
-        <v>979.5</v>
+        <v>992.5600000000001</v>
       </c>
       <c r="G77">
         <v>27</v>
@@ -7601,37 +7601,37 @@
         <v>17.75</v>
       </c>
       <c r="M77">
-        <v>230.9661</v>
+        <v>234.045648</v>
       </c>
       <c r="N77">
-        <v>-213.2161</v>
+        <v>-216.295648</v>
       </c>
       <c r="O77">
-        <v>-31.982415</v>
+        <v>-32.4443472</v>
       </c>
       <c r="P77">
-        <v>-181.233685</v>
+        <v>-183.8513008</v>
       </c>
       <c r="Q77">
-        <v>-175.233685</v>
+        <v>-177.8513008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2759376563094286</v>
+        <v>0.2855267253223215</v>
       </c>
       <c r="T77">
-        <v>4.365626299064614</v>
+        <v>4.547527394858974</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01152766574835008</v>
+        <v>0.01137598593587179</v>
       </c>
       <c r="W77">
-        <v>0.2330817764165391</v>
+        <v>0.2331175425163214</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0768511049890005</v>
+        <v>0.07583990623914527</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2456957463897615</v>
+        <v>0.2475957463897615</v>
       </c>
       <c r="C78">
-        <v>-596.253027774211</v>
+        <v>-612.7902232046524</v>
       </c>
       <c r="D78">
-        <v>369.3069722257891</v>
+        <v>365.8297767953476</v>
       </c>
       <c r="E78">
-        <v>901.36</v>
+        <v>914.42</v>
       </c>
       <c r="F78">
-        <v>992.5600000000001</v>
+        <v>1005.62</v>
       </c>
       <c r="G78">
         <v>27</v>
@@ -7683,37 +7683,37 @@
         <v>17.75</v>
       </c>
       <c r="M78">
-        <v>234.045648</v>
+        <v>237.125196</v>
       </c>
       <c r="N78">
-        <v>-216.295648</v>
+        <v>-219.375196</v>
       </c>
       <c r="O78">
-        <v>-32.4443472</v>
+        <v>-32.9062794</v>
       </c>
       <c r="P78">
-        <v>-183.8513008</v>
+        <v>-186.4689166</v>
       </c>
       <c r="Q78">
-        <v>-177.8513008</v>
+        <v>-180.4689166</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2855267253223215</v>
+        <v>0.295949626423292</v>
       </c>
       <c r="T78">
-        <v>4.547527394858974</v>
+        <v>4.745245977244146</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01137598593587179</v>
+        <v>0.01122824585878255</v>
       </c>
       <c r="W78">
-        <v>0.2331175425163214</v>
+        <v>0.2331523796264991</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07583990623914527</v>
+        <v>0.07485497239188366</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2475957463897615</v>
+        <v>0.2494957463897614</v>
       </c>
       <c r="C79">
-        <v>-612.7902232046524</v>
+        <v>-629.2625506009308</v>
       </c>
       <c r="D79">
-        <v>365.8297767953476</v>
+        <v>362.4174493990693</v>
       </c>
       <c r="E79">
-        <v>914.42</v>
+        <v>927.48</v>
       </c>
       <c r="F79">
-        <v>1005.62</v>
+        <v>1018.68</v>
       </c>
       <c r="G79">
         <v>27</v>
@@ -7765,37 +7765,37 @@
         <v>17.75</v>
       </c>
       <c r="M79">
-        <v>237.125196</v>
+        <v>240.204744</v>
       </c>
       <c r="N79">
-        <v>-219.375196</v>
+        <v>-222.454744</v>
       </c>
       <c r="O79">
-        <v>-32.9062794</v>
+        <v>-33.3682116</v>
       </c>
       <c r="P79">
-        <v>-186.4689166</v>
+        <v>-189.0865324</v>
       </c>
       <c r="Q79">
-        <v>-180.4689166</v>
+        <v>-183.0865324</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.295949626423292</v>
+        <v>0.3073200639879871</v>
       </c>
       <c r="T79">
-        <v>4.745245977244146</v>
+        <v>4.960938976209788</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01122824585878255</v>
+        <v>0.01108429398879815</v>
       </c>
       <c r="W79">
-        <v>0.2331523796264991</v>
+        <v>0.2331863234774414</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07485497239188366</v>
+        <v>0.0738952932586544</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2494957463897614</v>
+        <v>0.2513957463897615</v>
       </c>
       <c r="C80">
-        <v>-629.2625506009308</v>
+        <v>-645.6718083844689</v>
       </c>
       <c r="D80">
-        <v>362.4174493990693</v>
+        <v>359.068191615531</v>
       </c>
       <c r="E80">
-        <v>927.48</v>
+        <v>940.54</v>
       </c>
       <c r="F80">
-        <v>1018.68</v>
+        <v>1031.74</v>
       </c>
       <c r="G80">
         <v>27</v>
@@ -7847,37 +7847,37 @@
         <v>17.75</v>
       </c>
       <c r="M80">
-        <v>240.204744</v>
+        <v>243.284292</v>
       </c>
       <c r="N80">
-        <v>-222.454744</v>
+        <v>-225.534292</v>
       </c>
       <c r="O80">
-        <v>-33.3682116</v>
+        <v>-33.8301438</v>
       </c>
       <c r="P80">
-        <v>-189.0865324</v>
+        <v>-191.7041482</v>
       </c>
       <c r="Q80">
-        <v>-183.0865324</v>
+        <v>-185.7041482</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3073200639879871</v>
+        <v>0.3197734003683674</v>
       </c>
       <c r="T80">
-        <v>4.960938976209788</v>
+        <v>5.197174165553113</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01108429398879815</v>
+        <v>0.01094398646995261</v>
       </c>
       <c r="W80">
-        <v>0.2331863234774414</v>
+        <v>0.2332194079903852</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0738952932586544</v>
+        <v>0.07295990979968403</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2513957463897615</v>
+        <v>0.2532957463897615</v>
       </c>
       <c r="C81">
-        <v>-645.6718083844689</v>
+        <v>-662.019729105446</v>
       </c>
       <c r="D81">
-        <v>359.068191615531</v>
+        <v>355.780270894554</v>
       </c>
       <c r="E81">
-        <v>940.54</v>
+        <v>953.5999999999999</v>
       </c>
       <c r="F81">
-        <v>1031.74</v>
+        <v>1044.8</v>
       </c>
       <c r="G81">
         <v>27</v>
@@ -7929,37 +7929,37 @@
         <v>17.75</v>
       </c>
       <c r="M81">
-        <v>243.284292</v>
+        <v>246.36384</v>
       </c>
       <c r="N81">
-        <v>-225.534292</v>
+        <v>-228.61384</v>
       </c>
       <c r="O81">
-        <v>-33.8301438</v>
+        <v>-34.292076</v>
       </c>
       <c r="P81">
-        <v>-191.7041482</v>
+        <v>-194.321764</v>
       </c>
       <c r="Q81">
-        <v>-185.7041482</v>
+        <v>-188.321764</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3197734003683674</v>
+        <v>0.3334720703867858</v>
       </c>
       <c r="T81">
-        <v>5.197174165553113</v>
+        <v>5.457032873830769</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01094398646995261</v>
+        <v>0.0108071866390782</v>
       </c>
       <c r="W81">
-        <v>0.2332194079903852</v>
+        <v>0.2332516653905054</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07295990979968403</v>
+        <v>0.07204791092718799</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2532957463897615</v>
+        <v>0.2551957463897614</v>
       </c>
       <c r="C82">
-        <v>-662.019729105446</v>
+        <v>-678.3079824312869</v>
       </c>
       <c r="D82">
-        <v>355.780270894554</v>
+        <v>352.5520175687133</v>
       </c>
       <c r="E82">
-        <v>953.5999999999999</v>
+        <v>966.6600000000001</v>
       </c>
       <c r="F82">
-        <v>1044.8</v>
+        <v>1057.86</v>
       </c>
       <c r="G82">
         <v>27</v>
@@ -8011,37 +8011,37 @@
         <v>17.75</v>
       </c>
       <c r="M82">
-        <v>246.36384</v>
+        <v>249.443388</v>
       </c>
       <c r="N82">
-        <v>-228.61384</v>
+        <v>-231.693388</v>
       </c>
       <c r="O82">
-        <v>-34.292076</v>
+        <v>-34.7540082</v>
       </c>
       <c r="P82">
-        <v>-194.321764</v>
+        <v>-196.9393798</v>
       </c>
       <c r="Q82">
-        <v>-188.321764</v>
+        <v>-190.9393798</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3334720703867858</v>
+        <v>0.3486127056703009</v>
       </c>
       <c r="T82">
-        <v>5.457032873830769</v>
+        <v>5.744245130348178</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0108071866390782</v>
+        <v>0.01067376458180563</v>
       </c>
       <c r="W82">
-        <v>0.2332516653905054</v>
+        <v>0.2332831263116102</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07204791092718799</v>
+        <v>0.07115843054537085</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2551957463897614</v>
+        <v>0.2570957463897615</v>
       </c>
       <c r="C83">
-        <v>-678.3079824312869</v>
+        <v>-694.5381779739123</v>
       </c>
       <c r="D83">
-        <v>352.5520175687133</v>
+        <v>349.3818220260877</v>
       </c>
       <c r="E83">
-        <v>966.6600000000001</v>
+        <v>979.72</v>
       </c>
       <c r="F83">
-        <v>1057.86</v>
+        <v>1070.92</v>
       </c>
       <c r="G83">
         <v>27</v>
@@ -8093,37 +8093,37 @@
         <v>17.75</v>
       </c>
       <c r="M83">
-        <v>249.443388</v>
+        <v>252.522936</v>
       </c>
       <c r="N83">
-        <v>-231.693388</v>
+        <v>-234.772936</v>
       </c>
       <c r="O83">
-        <v>-34.7540082</v>
+        <v>-35.2159404</v>
       </c>
       <c r="P83">
-        <v>-196.9393798</v>
+        <v>-199.5569956</v>
       </c>
       <c r="Q83">
-        <v>-190.9393798</v>
+        <v>-193.5569956</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3486127056703009</v>
+        <v>0.3654356337630953</v>
       </c>
       <c r="T83">
-        <v>5.744245130348178</v>
+        <v>6.063369859811965</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01067376458180563</v>
+        <v>0.0105435967210519</v>
       </c>
       <c r="W83">
-        <v>0.2332831263116102</v>
+        <v>0.233313819893176</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07115843054537085</v>
+        <v>0.07029064480701275</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2570957463897615</v>
+        <v>0.2589957463897614</v>
       </c>
       <c r="C84">
-        <v>-694.5381779739123</v>
+        <v>-710.7118679658128</v>
       </c>
       <c r="D84">
-        <v>349.3818220260877</v>
+        <v>346.2681320341873</v>
       </c>
       <c r="E84">
-        <v>979.72</v>
+        <v>992.78</v>
       </c>
       <c r="F84">
-        <v>1070.92</v>
+        <v>1083.98</v>
       </c>
       <c r="G84">
         <v>27</v>
@@ -8175,37 +8175,37 @@
         <v>17.75</v>
       </c>
       <c r="M84">
-        <v>252.522936</v>
+        <v>255.602484</v>
       </c>
       <c r="N84">
-        <v>-234.772936</v>
+        <v>-237.852484</v>
       </c>
       <c r="O84">
-        <v>-35.2159404</v>
+        <v>-35.6778726</v>
       </c>
       <c r="P84">
-        <v>-199.5569956</v>
+        <v>-202.1746114</v>
       </c>
       <c r="Q84">
-        <v>-193.5569956</v>
+        <v>-196.1746114</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3654356337630953</v>
+        <v>0.3842377298668069</v>
       </c>
       <c r="T84">
-        <v>6.063369859811965</v>
+        <v>6.420038675095022</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0105435967210519</v>
+        <v>0.0104165654352561</v>
       </c>
       <c r="W84">
-        <v>0.233313819893176</v>
+        <v>0.2333437738703666</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07029064480701275</v>
+        <v>0.06944376956837395</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2589957463897614</v>
+        <v>0.2608957463897615</v>
       </c>
       <c r="C85">
-        <v>-710.7118679658128</v>
+        <v>-726.8305497942895</v>
       </c>
       <c r="D85">
-        <v>346.2681320341873</v>
+        <v>343.2094502057107</v>
       </c>
       <c r="E85">
-        <v>992.78</v>
+        <v>1005.84</v>
       </c>
       <c r="F85">
-        <v>1083.98</v>
+        <v>1097.04</v>
       </c>
       <c r="G85">
         <v>27</v>
@@ -8257,37 +8257,37 @@
         <v>17.75</v>
       </c>
       <c r="M85">
-        <v>255.602484</v>
+        <v>258.682032</v>
       </c>
       <c r="N85">
-        <v>-237.852484</v>
+        <v>-240.932032</v>
       </c>
       <c r="O85">
-        <v>-35.6778726</v>
+        <v>-36.13980480000001</v>
       </c>
       <c r="P85">
-        <v>-202.1746114</v>
+        <v>-204.7922272</v>
       </c>
       <c r="Q85">
-        <v>-196.1746114</v>
+        <v>-198.7922272</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3842377298668069</v>
+        <v>0.4053900879834824</v>
       </c>
       <c r="T85">
-        <v>6.420038675095022</v>
+        <v>6.821291092288463</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0104165654352561</v>
+        <v>0.010292558703884</v>
       </c>
       <c r="W85">
-        <v>0.2333437738703666</v>
+        <v>0.2333730146576242</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06944376956837395</v>
+        <v>0.06861705802589335</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2608957463897614</v>
+        <v>0.2627957463897614</v>
       </c>
       <c r="C86">
-        <v>-726.8305497942891</v>
+        <v>-742.895668402557</v>
       </c>
       <c r="D86">
-        <v>343.2094502057108</v>
+        <v>340.2043315974429</v>
       </c>
       <c r="E86">
-        <v>1005.84</v>
+        <v>1018.9</v>
       </c>
       <c r="F86">
-        <v>1097.04</v>
+        <v>1110.1</v>
       </c>
       <c r="G86">
         <v>27</v>
@@ -8339,37 +8339,37 @@
         <v>17.75</v>
       </c>
       <c r="M86">
-        <v>258.682032</v>
+        <v>261.76158</v>
       </c>
       <c r="N86">
-        <v>-240.932032</v>
+        <v>-244.01158</v>
       </c>
       <c r="O86">
-        <v>-36.1398048</v>
+        <v>-36.60173699999999</v>
       </c>
       <c r="P86">
-        <v>-204.7922272</v>
+        <v>-207.409843</v>
       </c>
       <c r="Q86">
-        <v>-198.7922272</v>
+        <v>-201.409843</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4053900879834821</v>
+        <v>0.4293627605157143</v>
       </c>
       <c r="T86">
-        <v>6.821291092288458</v>
+        <v>7.276043831774356</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.010292558703884</v>
+        <v>0.01017146977795596</v>
       </c>
       <c r="W86">
-        <v>0.2333730146576242</v>
+        <v>0.233401567426358</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06861705802589335</v>
+        <v>0.06780979851970637</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2627957463897614</v>
+        <v>0.2646957463897615</v>
       </c>
       <c r="C87">
-        <v>-742.895668402557</v>
+        <v>-758.9086185658016</v>
       </c>
       <c r="D87">
-        <v>340.2043315974429</v>
+        <v>337.2513814341985</v>
       </c>
       <c r="E87">
-        <v>1018.9</v>
+        <v>1031.96</v>
       </c>
       <c r="F87">
-        <v>1110.1</v>
+        <v>1123.16</v>
       </c>
       <c r="G87">
         <v>27</v>
@@ -8421,37 +8421,37 @@
         <v>17.75</v>
       </c>
       <c r="M87">
-        <v>261.76158</v>
+        <v>264.841128</v>
       </c>
       <c r="N87">
-        <v>-244.01158</v>
+        <v>-247.091128</v>
       </c>
       <c r="O87">
-        <v>-36.60173699999999</v>
+        <v>-37.0636692</v>
       </c>
       <c r="P87">
-        <v>-207.409843</v>
+        <v>-210.0274588</v>
       </c>
       <c r="Q87">
-        <v>-201.409843</v>
+        <v>-204.0274588</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4293627605157143</v>
+        <v>0.4567601005525511</v>
       </c>
       <c r="T87">
-        <v>7.276043831774356</v>
+        <v>7.795761248329668</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01017146977795596</v>
+        <v>0.01005319687356112</v>
       </c>
       <c r="W87">
-        <v>0.233401567426358</v>
+        <v>0.2334294561772143</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06780979851970637</v>
+        <v>0.06702131249040744</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2646957463897615</v>
+        <v>0.2665957463897615</v>
       </c>
       <c r="C88">
-        <v>-758.9086185658016</v>
+        <v>-774.8707470497164</v>
       </c>
       <c r="D88">
-        <v>337.2513814341985</v>
+        <v>334.3492529502836</v>
       </c>
       <c r="E88">
-        <v>1031.96</v>
+        <v>1045.02</v>
       </c>
       <c r="F88">
-        <v>1123.16</v>
+        <v>1136.22</v>
       </c>
       <c r="G88">
         <v>27</v>
@@ -8503,37 +8503,37 @@
         <v>17.75</v>
       </c>
       <c r="M88">
-        <v>264.841128</v>
+        <v>267.920676</v>
       </c>
       <c r="N88">
-        <v>-247.091128</v>
+        <v>-250.170676</v>
       </c>
       <c r="O88">
-        <v>-37.0636692</v>
+        <v>-37.5256014</v>
       </c>
       <c r="P88">
-        <v>-210.0274588</v>
+        <v>-212.6450746</v>
       </c>
       <c r="Q88">
-        <v>-204.0274588</v>
+        <v>-206.6450746</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4567601005525511</v>
+        <v>0.4883724159796703</v>
       </c>
       <c r="T88">
-        <v>7.795761248329668</v>
+        <v>8.395435190508872</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01005319687356112</v>
+        <v>0.009937642886508691</v>
       </c>
       <c r="W88">
-        <v>0.2334294561772143</v>
+        <v>0.2334567038073613</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06702131249040744</v>
+        <v>0.06625095257672464</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2665957463897615</v>
+        <v>0.2684957463897615</v>
       </c>
       <c r="C89">
-        <v>-774.8707470497164</v>
+        <v>-790.7833546585466</v>
       </c>
       <c r="D89">
-        <v>334.3492529502836</v>
+        <v>331.4966453414534</v>
       </c>
       <c r="E89">
-        <v>1045.02</v>
+        <v>1058.08</v>
       </c>
       <c r="F89">
-        <v>1136.22</v>
+        <v>1149.28</v>
       </c>
       <c r="G89">
         <v>27</v>
@@ -8585,37 +8585,37 @@
         <v>17.75</v>
       </c>
       <c r="M89">
-        <v>267.920676</v>
+        <v>271.000224</v>
       </c>
       <c r="N89">
-        <v>-250.170676</v>
+        <v>-253.250224</v>
       </c>
       <c r="O89">
-        <v>-37.5256014</v>
+        <v>-37.9875336</v>
       </c>
       <c r="P89">
-        <v>-212.6450746</v>
+        <v>-215.2626904</v>
       </c>
       <c r="Q89">
-        <v>-206.6450746</v>
+        <v>-209.2626904</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4883724159796703</v>
+        <v>0.525253450644643</v>
       </c>
       <c r="T89">
-        <v>8.395435190508872</v>
+        <v>9.095054789717947</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.009937642886508691</v>
+        <v>0.00982471512643473</v>
       </c>
       <c r="W89">
-        <v>0.2334567038073613</v>
+        <v>0.2334833321731867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06625095257672464</v>
+        <v>0.0654981008428982</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2684957463897615</v>
+        <v>0.2703957463897614</v>
       </c>
       <c r="C90">
-        <v>-790.7833546585466</v>
+        <v>-806.6476981791745</v>
       </c>
       <c r="D90">
-        <v>331.4966453414534</v>
+        <v>328.6923018208254</v>
       </c>
       <c r="E90">
-        <v>1058.08</v>
+        <v>1071.14</v>
       </c>
       <c r="F90">
-        <v>1149.28</v>
+        <v>1162.34</v>
       </c>
       <c r="G90">
         <v>27</v>
@@ -8667,37 +8667,37 @@
         <v>17.75</v>
       </c>
       <c r="M90">
-        <v>271.000224</v>
+        <v>274.079772</v>
       </c>
       <c r="N90">
-        <v>-253.250224</v>
+        <v>-256.329772</v>
       </c>
       <c r="O90">
-        <v>-37.9875336</v>
+        <v>-38.4494658</v>
       </c>
       <c r="P90">
-        <v>-215.2626904</v>
+        <v>-217.8803062</v>
       </c>
       <c r="Q90">
-        <v>-209.2626904</v>
+        <v>-211.8803062</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.525253450644643</v>
+        <v>0.5688401279759741</v>
       </c>
       <c r="T90">
-        <v>9.095054789717947</v>
+        <v>9.921877952419576</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.00982471512643473</v>
+        <v>0.009714325068834339</v>
       </c>
       <c r="W90">
-        <v>0.2334833321731867</v>
+        <v>0.2335093621487689</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0654981008428982</v>
+        <v>0.06476216712556226</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2703957463897614</v>
+        <v>0.2722957463897615</v>
       </c>
       <c r="C91">
-        <v>-806.6476981791745</v>
+        <v>-822.4649922273591</v>
       </c>
       <c r="D91">
-        <v>328.6923018208254</v>
+        <v>325.935007772641</v>
       </c>
       <c r="E91">
-        <v>1071.14</v>
+        <v>1084.2</v>
       </c>
       <c r="F91">
-        <v>1162.34</v>
+        <v>1175.4</v>
       </c>
       <c r="G91">
         <v>27</v>
@@ -8749,37 +8749,37 @@
         <v>17.75</v>
       </c>
       <c r="M91">
-        <v>274.079772</v>
+        <v>277.15932</v>
       </c>
       <c r="N91">
-        <v>-256.329772</v>
+        <v>-259.40932</v>
       </c>
       <c r="O91">
-        <v>-38.4494658</v>
+        <v>-38.91139800000001</v>
       </c>
       <c r="P91">
-        <v>-217.8803062</v>
+        <v>-220.497922</v>
       </c>
       <c r="Q91">
-        <v>-211.8803062</v>
+        <v>-214.497922</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5688401279759741</v>
+        <v>0.6211441407735716</v>
       </c>
       <c r="T91">
-        <v>9.921877952419576</v>
+        <v>10.91406574766154</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.009714325068834339</v>
+        <v>0.009606388123625067</v>
       </c>
       <c r="W91">
-        <v>0.2335093621487689</v>
+        <v>0.2335348136804492</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06476216712556226</v>
+        <v>0.0640425874908338</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2722957463897615</v>
+        <v>0.2741957463897614</v>
       </c>
       <c r="C92">
-        <v>-822.4649922273591</v>
+        <v>-838.2364110018191</v>
       </c>
       <c r="D92">
-        <v>325.935007772641</v>
+        <v>323.223588998181</v>
       </c>
       <c r="E92">
-        <v>1084.2</v>
+        <v>1097.26</v>
       </c>
       <c r="F92">
-        <v>1175.4</v>
+        <v>1188.46</v>
       </c>
       <c r="G92">
         <v>27</v>
@@ -8831,37 +8831,37 @@
         <v>17.75</v>
       </c>
       <c r="M92">
-        <v>277.15932</v>
+        <v>280.238868</v>
       </c>
       <c r="N92">
-        <v>-259.40932</v>
+        <v>-262.488868</v>
       </c>
       <c r="O92">
-        <v>-38.91139800000001</v>
+        <v>-39.37333020000001</v>
       </c>
       <c r="P92">
-        <v>-220.497922</v>
+        <v>-223.1155378</v>
       </c>
       <c r="Q92">
-        <v>-214.497922</v>
+        <v>-217.1155378</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6211441407735716</v>
+        <v>0.6850712675261906</v>
       </c>
       <c r="T92">
-        <v>10.91406574766154</v>
+        <v>12.12673971962393</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.009606388123625067</v>
+        <v>0.009500823418969847</v>
       </c>
       <c r="W92">
-        <v>0.2335348136804492</v>
+        <v>0.2335597058378069</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.0640425874908338</v>
+        <v>0.0633388227931323</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2741957463897614</v>
+        <v>0.2760957463897614</v>
       </c>
       <c r="C93">
-        <v>-838.2364110018191</v>
+        <v>-853.9630899514909</v>
       </c>
       <c r="D93">
-        <v>323.223588998181</v>
+        <v>320.5569100485091</v>
       </c>
       <c r="E93">
-        <v>1097.26</v>
+        <v>1110.32</v>
       </c>
       <c r="F93">
-        <v>1188.46</v>
+        <v>1201.52</v>
       </c>
       <c r="G93">
         <v>27</v>
@@ -8913,37 +8913,37 @@
         <v>17.75</v>
       </c>
       <c r="M93">
-        <v>280.238868</v>
+        <v>283.318416</v>
       </c>
       <c r="N93">
-        <v>-262.488868</v>
+        <v>-265.568416</v>
       </c>
       <c r="O93">
-        <v>-39.37333020000001</v>
+        <v>-39.8352624</v>
       </c>
       <c r="P93">
-        <v>-223.1155378</v>
+        <v>-225.7331536</v>
       </c>
       <c r="Q93">
-        <v>-217.1155378</v>
+        <v>-219.7331536</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6850712675261906</v>
+        <v>0.7649801759669647</v>
       </c>
       <c r="T93">
-        <v>12.12673971962393</v>
+        <v>13.64258218457693</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.009500823418969847</v>
+        <v>0.009397553599198435</v>
       </c>
       <c r="W93">
-        <v>0.2335597058378069</v>
+        <v>0.233584056861309</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.0633388227931323</v>
+        <v>0.06265035732798963</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2760957463897614</v>
+        <v>0.2779957463897614</v>
       </c>
       <c r="C94">
-        <v>-853.9630899514909</v>
+        <v>-869.6461273609266</v>
       </c>
       <c r="D94">
-        <v>320.5569100485091</v>
+        <v>317.9338726390735</v>
       </c>
       <c r="E94">
-        <v>1110.32</v>
+        <v>1123.38</v>
       </c>
       <c r="F94">
-        <v>1201.52</v>
+        <v>1214.58</v>
       </c>
       <c r="G94">
         <v>27</v>
@@ -8995,37 +8995,37 @@
         <v>17.75</v>
       </c>
       <c r="M94">
-        <v>283.318416</v>
+        <v>286.3979640000001</v>
       </c>
       <c r="N94">
-        <v>-265.568416</v>
+        <v>-268.6479640000001</v>
       </c>
       <c r="O94">
-        <v>-39.8352624</v>
+        <v>-40.2971946</v>
       </c>
       <c r="P94">
-        <v>-225.7331536</v>
+        <v>-228.3507694</v>
       </c>
       <c r="Q94">
-        <v>-219.7331536</v>
+        <v>-222.3507694</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7649801759669647</v>
+        <v>0.8677202011051026</v>
       </c>
       <c r="T94">
-        <v>13.64258218457693</v>
+        <v>15.59152249665935</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.009397553599198435</v>
+        <v>0.009296504635766194</v>
       </c>
       <c r="W94">
-        <v>0.233584056861309</v>
+        <v>0.2336078842068864</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06265035732798963</v>
+        <v>0.0619766975717746</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2779957463897614</v>
+        <v>0.2798957463897614</v>
       </c>
       <c r="C95">
-        <v>-869.6461273609266</v>
+        <v>-885.2865858584873</v>
       </c>
       <c r="D95">
-        <v>317.9338726390735</v>
+        <v>315.3534141415128</v>
       </c>
       <c r="E95">
-        <v>1123.38</v>
+        <v>1136.44</v>
       </c>
       <c r="F95">
-        <v>1214.58</v>
+        <v>1227.64</v>
       </c>
       <c r="G95">
         <v>27</v>
@@ -9077,37 +9077,37 @@
         <v>17.75</v>
       </c>
       <c r="M95">
-        <v>286.3979640000001</v>
+        <v>289.477512</v>
       </c>
       <c r="N95">
-        <v>-268.6479640000001</v>
+        <v>-271.727512</v>
       </c>
       <c r="O95">
-        <v>-40.2971946</v>
+        <v>-40.7591268</v>
       </c>
       <c r="P95">
-        <v>-228.3507694</v>
+        <v>-230.9683852000001</v>
       </c>
       <c r="Q95">
-        <v>-222.3507694</v>
+        <v>-224.9683852000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8677202011051026</v>
+        <v>1.004706901289287</v>
       </c>
       <c r="T95">
-        <v>15.59152249665935</v>
+        <v>18.19010957943591</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.009296504635766194</v>
+        <v>0.009197605650279319</v>
       </c>
       <c r="W95">
-        <v>0.2336078842068864</v>
+        <v>0.2336312045876641</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.0619766975717746</v>
+        <v>0.06131737100186219</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2798957463897614</v>
+        <v>0.2817957463897615</v>
       </c>
       <c r="C96">
-        <v>-885.2865858584873</v>
+        <v>-900.8854938516816</v>
       </c>
       <c r="D96">
-        <v>315.3534141415128</v>
+        <v>312.8145061483184</v>
       </c>
       <c r="E96">
-        <v>1136.44</v>
+        <v>1149.5</v>
       </c>
       <c r="F96">
-        <v>1227.64</v>
+        <v>1240.7</v>
       </c>
       <c r="G96">
         <v>27</v>
@@ -9159,37 +9159,37 @@
         <v>17.75</v>
       </c>
       <c r="M96">
-        <v>289.477512</v>
+        <v>292.55706</v>
       </c>
       <c r="N96">
-        <v>-271.727512</v>
+        <v>-274.80706</v>
       </c>
       <c r="O96">
-        <v>-40.7591268</v>
+        <v>-41.221059</v>
       </c>
       <c r="P96">
-        <v>-230.9683852000001</v>
+        <v>-233.586001</v>
       </c>
       <c r="Q96">
-        <v>-224.9683852000001</v>
+        <v>-227.586001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.004706901289287</v>
+        <v>1.196488281547144</v>
       </c>
       <c r="T96">
-        <v>18.19010957943591</v>
+        <v>21.8281314953231</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.009197605650279319</v>
+        <v>0.009100788748697432</v>
       </c>
       <c r="W96">
-        <v>0.2336312045876641</v>
+        <v>0.2336540340130571</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06131737100186219</v>
+        <v>0.06067192499131624</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2817957463897615</v>
+        <v>0.2836957463897615</v>
       </c>
       <c r="C97">
-        <v>-900.8854938516816</v>
+        <v>-916.4438468937241</v>
       </c>
       <c r="D97">
-        <v>312.8145061483184</v>
+        <v>310.3161531062759</v>
       </c>
       <c r="E97">
-        <v>1149.5</v>
+        <v>1162.56</v>
       </c>
       <c r="F97">
-        <v>1240.7</v>
+        <v>1253.76</v>
       </c>
       <c r="G97">
         <v>27</v>
@@ -9241,37 +9241,37 @@
         <v>17.75</v>
       </c>
       <c r="M97">
-        <v>292.55706</v>
+        <v>295.636608</v>
       </c>
       <c r="N97">
-        <v>-274.80706</v>
+        <v>-277.886608</v>
       </c>
       <c r="O97">
-        <v>-41.221059</v>
+        <v>-41.6829912</v>
       </c>
       <c r="P97">
-        <v>-233.586001</v>
+        <v>-236.2036168</v>
       </c>
       <c r="Q97">
-        <v>-227.586001</v>
+        <v>-230.2036168</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.196488281547144</v>
+        <v>1.484160351933931</v>
       </c>
       <c r="T97">
-        <v>21.8281314953231</v>
+        <v>27.28516436915389</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.009100788748697432</v>
+        <v>0.009005988865898502</v>
       </c>
       <c r="W97">
-        <v>0.2336540340130571</v>
+        <v>0.2336763878254211</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.06067192499131624</v>
+        <v>0.06003992577265671</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2836957463897615</v>
+        <v>0.2855957463897615</v>
       </c>
       <c r="C98">
-        <v>-916.4438468937241</v>
+        <v>-931.9626089851231</v>
       </c>
       <c r="D98">
-        <v>310.3161531062759</v>
+        <v>307.8573910148768</v>
       </c>
       <c r="E98">
-        <v>1162.56</v>
+        <v>1175.62</v>
       </c>
       <c r="F98">
-        <v>1253.76</v>
+        <v>1266.82</v>
       </c>
       <c r="G98">
         <v>27</v>
@@ -9323,37 +9323,37 @@
         <v>17.75</v>
       </c>
       <c r="M98">
-        <v>295.636608</v>
+        <v>298.716156</v>
       </c>
       <c r="N98">
-        <v>-277.886608</v>
+        <v>-280.966156</v>
       </c>
       <c r="O98">
-        <v>-41.6829912</v>
+        <v>-42.1449234</v>
       </c>
       <c r="P98">
-        <v>-236.2036168</v>
+        <v>-238.8212326</v>
       </c>
       <c r="Q98">
-        <v>-230.2036168</v>
+        <v>-232.8212326</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.484160351933927</v>
+        <v>1.96361380257857</v>
       </c>
       <c r="T98">
-        <v>27.28516436915381</v>
+        <v>36.38021915887175</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.009005988865898502</v>
+        <v>0.008913143619858311</v>
       </c>
       <c r="W98">
-        <v>0.2336763878254211</v>
+        <v>0.2336982807344374</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06003992577265671</v>
+        <v>0.05942095746572207</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2855957463897615</v>
+        <v>0.2874957463897614</v>
       </c>
       <c r="C99">
-        <v>-931.9626089851231</v>
+        <v>-947.4427138138817</v>
       </c>
       <c r="D99">
-        <v>307.8573910148768</v>
+        <v>305.4372861861182</v>
       </c>
       <c r="E99">
-        <v>1175.62</v>
+        <v>1188.68</v>
       </c>
       <c r="F99">
-        <v>1266.82</v>
+        <v>1279.88</v>
       </c>
       <c r="G99">
         <v>27</v>
@@ -9405,37 +9405,37 @@
         <v>17.75</v>
       </c>
       <c r="M99">
-        <v>298.716156</v>
+        <v>301.795704</v>
       </c>
       <c r="N99">
-        <v>-280.966156</v>
+        <v>-284.045704</v>
       </c>
       <c r="O99">
-        <v>-42.1449234</v>
+        <v>-42.6068556</v>
       </c>
       <c r="P99">
-        <v>-238.8212326</v>
+        <v>-241.4388484</v>
       </c>
       <c r="Q99">
-        <v>-232.8212326</v>
+        <v>-235.4388484</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.96361380257857</v>
+        <v>2.922520703867855</v>
       </c>
       <c r="T99">
-        <v>36.38021915887175</v>
+        <v>54.57032873830762</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.008913143619858311</v>
+        <v>0.008822193174757716</v>
       </c>
       <c r="W99">
-        <v>0.2336982807344374</v>
+        <v>0.2337197268493921</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05942095746572207</v>
+        <v>0.05881462116505143</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2874957463897614</v>
+        <v>0.2893957463897615</v>
       </c>
       <c r="C100">
-        <v>-947.4427138138817</v>
+        <v>-962.8850659376545</v>
       </c>
       <c r="D100">
-        <v>305.4372861861182</v>
+        <v>303.0549340623455</v>
       </c>
       <c r="E100">
-        <v>1188.68</v>
+        <v>1201.74</v>
       </c>
       <c r="F100">
-        <v>1279.88</v>
+        <v>1292.94</v>
       </c>
       <c r="G100">
         <v>27</v>
@@ -9487,37 +9487,37 @@
         <v>17.75</v>
       </c>
       <c r="M100">
-        <v>301.795704</v>
+        <v>304.875252</v>
       </c>
       <c r="N100">
-        <v>-284.045704</v>
+        <v>-287.125252</v>
       </c>
       <c r="O100">
-        <v>-42.6068556</v>
+        <v>-43.0687878</v>
       </c>
       <c r="P100">
-        <v>-241.4388484</v>
+        <v>-244.0564642000001</v>
       </c>
       <c r="Q100">
-        <v>-235.4388484</v>
+        <v>-238.0564642000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.922520703867855</v>
+        <v>5.79924140773571</v>
       </c>
       <c r="T100">
-        <v>54.57032873830762</v>
+        <v>109.1406574766152</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.008822193174757716</v>
+        <v>0.008733080112386424</v>
       </c>
       <c r="W100">
-        <v>0.2337197268493921</v>
+        <v>0.2337407397094993</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05881462116505143</v>
+        <v>0.05822053408257621</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2893957463897615</v>
-      </c>
-      <c r="C101">
-        <v>-962.8850659376545</v>
-      </c>
-      <c r="D101">
-        <v>303.0549340623455</v>
-      </c>
-      <c r="E101">
-        <v>1201.74</v>
-      </c>
-      <c r="F101">
-        <v>1292.94</v>
-      </c>
-      <c r="G101">
-        <v>27</v>
-      </c>
-      <c r="H101">
-        <v>1214.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.75</v>
-      </c>
-      <c r="K101">
-        <v>6</v>
-      </c>
-      <c r="L101">
-        <v>17.75</v>
-      </c>
-      <c r="M101">
-        <v>304.875252</v>
-      </c>
-      <c r="N101">
-        <v>-287.125252</v>
-      </c>
-      <c r="O101">
-        <v>-43.0687878</v>
-      </c>
-      <c r="P101">
-        <v>-244.0564642000001</v>
-      </c>
-      <c r="Q101">
-        <v>-238.0564642000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.79924140773571</v>
-      </c>
-      <c r="T101">
-        <v>109.1406574766152</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.008733080112386424</v>
-      </c>
-      <c r="W101">
-        <v>0.2337407397094993</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05822053408257621</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
